--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_RMSEP.xlsx
@@ -214,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,13 +230,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,7 +239,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -254,112 +247,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -662,7 +580,9 @@
   <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -723,52 +643,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>256.62758695565992</v>
+        <v>254.8396153847788</v>
       </c>
       <c r="C2">
-        <v>288.11756738609978</v>
+        <v>288.00277910478218</v>
       </c>
       <c r="D2">
-        <v>255.2620075998822</v>
+        <v>254.32743711924559</v>
       </c>
       <c r="E2">
-        <v>249.50720005253609</v>
+        <v>248.51223729117709</v>
       </c>
       <c r="F2">
-        <v>242.24786163761109</v>
+        <v>241.9878516363826</v>
       </c>
       <c r="G2">
-        <v>244.93889383001749</v>
+        <v>245.24922387558311</v>
       </c>
       <c r="H2">
-        <v>242.58228448889929</v>
+        <v>241.26860014619149</v>
       </c>
       <c r="I2">
-        <v>243.942103151776</v>
+        <v>242.7509855430788</v>
       </c>
       <c r="J2">
-        <v>244.247908340896</v>
+        <v>243.2334362639441</v>
       </c>
       <c r="K2">
-        <v>242.606651813806</v>
+        <v>242.46669473278899</v>
       </c>
       <c r="L2">
-        <v>244.4186816571374</v>
+        <v>243.3122327118233</v>
       </c>
       <c r="M2">
-        <v>253.41976175937771</v>
+        <v>252.3774831911758</v>
       </c>
       <c r="N2">
-        <v>261.91912233124782</v>
+        <v>261.6451748996675</v>
       </c>
       <c r="O2">
-        <v>269.70857151118372</v>
+        <v>269.11559455272823</v>
       </c>
       <c r="P2">
-        <v>280.01379297603398</v>
+        <v>280.18125155433182</v>
       </c>
       <c r="Q2">
-        <v>272.19421447039639</v>
+        <v>272.49857921212117</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -776,52 +696,52 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>262.98112692232883</v>
+        <v>262.86936728461518</v>
       </c>
       <c r="C3">
-        <v>265.11210156821357</v>
+        <v>265.3360868800047</v>
       </c>
       <c r="D3">
-        <v>250.7651826049173</v>
+        <v>250.65026776909309</v>
       </c>
       <c r="E3">
-        <v>252.08974427119719</v>
+        <v>251.61323607944809</v>
       </c>
       <c r="F3">
-        <v>249.8453267704831</v>
+        <v>249.10607641981181</v>
       </c>
       <c r="G3">
-        <v>249.80886370311421</v>
+        <v>248.85070697864381</v>
       </c>
       <c r="H3">
-        <v>248.3834765877836</v>
+        <v>246.33993620924161</v>
       </c>
       <c r="I3">
-        <v>256.39739340605541</v>
+        <v>254.5839346137077</v>
       </c>
       <c r="J3">
-        <v>258.43446131668281</v>
+        <v>257.53333805852913</v>
       </c>
       <c r="K3">
-        <v>262.36538880566002</v>
+        <v>261.62328993807381</v>
       </c>
       <c r="L3">
-        <v>266.37856211611438</v>
+        <v>265.97615270918692</v>
       </c>
       <c r="M3">
-        <v>275.05912930932828</v>
+        <v>274.30856261085052</v>
       </c>
       <c r="N3">
-        <v>293.44416072522148</v>
+        <v>291.62424381677607</v>
       </c>
       <c r="O3">
-        <v>311.44342028646781</v>
+        <v>309.38617201777288</v>
       </c>
       <c r="P3">
-        <v>321.16391088958409</v>
+        <v>319.8943999093255</v>
       </c>
       <c r="Q3">
-        <v>331.86580957988838</v>
+        <v>331.73663245933568</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -829,52 +749,52 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>264.57279079294352</v>
+        <v>261.93271175084487</v>
       </c>
       <c r="C4">
-        <v>284.59286220749613</v>
+        <v>283.28719939984012</v>
       </c>
       <c r="D4">
-        <v>257.06648401409171</v>
+        <v>255.9395740231927</v>
       </c>
       <c r="E4">
-        <v>254.31554307019599</v>
+        <v>252.81585606728231</v>
       </c>
       <c r="F4">
-        <v>255.50112346642109</v>
+        <v>253.7015967785386</v>
       </c>
       <c r="G4">
-        <v>249.1870678871723</v>
+        <v>246.25120494574929</v>
       </c>
       <c r="H4">
-        <v>238.4010447745307</v>
+        <v>235.3880574291058</v>
       </c>
       <c r="I4">
-        <v>233.85178578343431</v>
+        <v>231.53078615796619</v>
       </c>
       <c r="J4">
-        <v>243.6541079916127</v>
+        <v>240.67665942042839</v>
       </c>
       <c r="K4">
-        <v>254.96913454203599</v>
+        <v>252.02724649887969</v>
       </c>
       <c r="L4">
-        <v>261.26083611758781</v>
+        <v>259.85009285220099</v>
       </c>
       <c r="M4">
-        <v>280.51709457565499</v>
+        <v>278.31983238335141</v>
       </c>
       <c r="N4">
-        <v>277.95948201825831</v>
+        <v>276.40736357787449</v>
       </c>
       <c r="O4">
-        <v>268.9598867722321</v>
+        <v>267.41217060483871</v>
       </c>
       <c r="P4">
-        <v>263.34369197815829</v>
+        <v>261.30566269378988</v>
       </c>
       <c r="Q4">
-        <v>262.94809207932769</v>
+        <v>260.59476673451002</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -882,52 +802,52 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>256.02816674471791</v>
+        <v>255.00603467320889</v>
       </c>
       <c r="C5">
-        <v>252.8601999142349</v>
+        <v>252.86806461560789</v>
       </c>
       <c r="D5">
-        <v>251.67497055918531</v>
+        <v>251.6194540677059</v>
       </c>
       <c r="E5">
-        <v>249.68902248743899</v>
+        <v>249.98590042330471</v>
       </c>
       <c r="F5">
-        <v>244.60149247560261</v>
+        <v>244.00863616537299</v>
       </c>
       <c r="G5">
-        <v>245.57941442712001</v>
+        <v>245.42288303244851</v>
       </c>
       <c r="H5">
-        <v>243.9580038070151</v>
+        <v>243.90269937583889</v>
       </c>
       <c r="I5">
-        <v>244.03089373391609</v>
+        <v>244.421794877948</v>
       </c>
       <c r="J5">
-        <v>251.0957679327073</v>
+        <v>252.42103837222791</v>
       </c>
       <c r="K5">
-        <v>259.54558535665342</v>
+        <v>260.51052656332479</v>
       </c>
       <c r="L5">
-        <v>269.27902195128701</v>
+        <v>269.76563020707329</v>
       </c>
       <c r="M5">
-        <v>274.74821828725442</v>
+        <v>277.86897251746927</v>
       </c>
       <c r="N5">
-        <v>278.37517183372239</v>
+        <v>281.21553790226938</v>
       </c>
       <c r="O5">
-        <v>272.65803440281258</v>
+        <v>274.6898758316392</v>
       </c>
       <c r="P5">
-        <v>270.01810686737667</v>
+        <v>273.24416398639607</v>
       </c>
       <c r="Q5">
-        <v>266.45007716140651</v>
+        <v>268.19087405167102</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -935,52 +855,52 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>254.34192506003441</v>
+        <v>254.2078443442515</v>
       </c>
       <c r="C6">
-        <v>252.7154741198338</v>
+        <v>252.00496448660471</v>
       </c>
       <c r="D6">
-        <v>252.09685847848229</v>
+        <v>250.96139647172279</v>
       </c>
       <c r="E6">
-        <v>250.5595156925641</v>
+        <v>249.4981779651302</v>
       </c>
       <c r="F6">
-        <v>247.83447888794291</v>
+        <v>247.01531787666329</v>
       </c>
       <c r="G6">
-        <v>239.0920796513758</v>
+        <v>239.53439443604779</v>
       </c>
       <c r="H6">
-        <v>243.76937010744939</v>
+        <v>243.49367463246719</v>
       </c>
       <c r="I6">
-        <v>245.2743445899068</v>
+        <v>245.5859925215924</v>
       </c>
       <c r="J6">
-        <v>257.20143156888878</v>
+        <v>257.36078261234758</v>
       </c>
       <c r="K6">
-        <v>268.14831230624361</v>
+        <v>268.1299966926544</v>
       </c>
       <c r="L6">
-        <v>273.76506650303497</v>
+        <v>274.12140200387228</v>
       </c>
       <c r="M6">
-        <v>281.74009191281851</v>
+        <v>281.6606602593713</v>
       </c>
       <c r="N6">
-        <v>282.31877346266862</v>
+        <v>281.89704864284198</v>
       </c>
       <c r="O6">
-        <v>285.37105108427022</v>
+        <v>285.46257912736661</v>
       </c>
       <c r="P6">
-        <v>280.33885667820471</v>
+        <v>280.89672482648109</v>
       </c>
       <c r="Q6">
-        <v>279.76620463020481</v>
+        <v>278.62867147060172</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -988,52 +908,52 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>248.469364522966</v>
+        <v>250.64327235865181</v>
       </c>
       <c r="C7">
-        <v>284.41421202355139</v>
+        <v>284.33566257872729</v>
       </c>
       <c r="D7">
-        <v>253.8566680771286</v>
+        <v>253.66270157609949</v>
       </c>
       <c r="E7">
-        <v>238.2836192500703</v>
+        <v>239.012250957405</v>
       </c>
       <c r="F7">
-        <v>228.8168813800153</v>
+        <v>229.5859160039407</v>
       </c>
       <c r="G7">
-        <v>226.94400405885281</v>
+        <v>227.90116021891791</v>
       </c>
       <c r="H7">
-        <v>227.59305205599901</v>
+        <v>228.17763663949859</v>
       </c>
       <c r="I7">
-        <v>230.93072607194259</v>
+        <v>230.69419597900961</v>
       </c>
       <c r="J7">
-        <v>230.45696166768869</v>
+        <v>229.6777342029427</v>
       </c>
       <c r="K7">
-        <v>239.3840495635358</v>
+        <v>238.62182361691649</v>
       </c>
       <c r="L7">
-        <v>251.63718517749709</v>
+        <v>249.29777274754389</v>
       </c>
       <c r="M7">
-        <v>257.78955762307032</v>
+        <v>255.62357634791351</v>
       </c>
       <c r="N7">
-        <v>266.54146465281679</v>
+        <v>264.90372293128689</v>
       </c>
       <c r="O7">
-        <v>267.24323488810251</v>
+        <v>265.01918732025212</v>
       </c>
       <c r="P7">
-        <v>261.54599159234488</v>
+        <v>259.44020924548261</v>
       </c>
       <c r="Q7">
-        <v>257.78789671930957</v>
+        <v>255.07273666426829</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1041,52 +961,52 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>261.53443518433511</v>
+        <v>264.25236841052492</v>
       </c>
       <c r="C8">
-        <v>273.2187024274852</v>
+        <v>273.75021062871878</v>
       </c>
       <c r="D8">
-        <v>258.16846904241868</v>
+        <v>258.34065409053977</v>
       </c>
       <c r="E8">
-        <v>244.56585245794261</v>
+        <v>245.1257254505588</v>
       </c>
       <c r="F8">
-        <v>242.63905321306879</v>
+        <v>243.08201975539581</v>
       </c>
       <c r="G8">
-        <v>241.66965621493571</v>
+        <v>242.14221240243549</v>
       </c>
       <c r="H8">
-        <v>242.09506554204859</v>
+        <v>242.23847297651639</v>
       </c>
       <c r="I8">
-        <v>238.1247660458265</v>
+        <v>239.0367102842379</v>
       </c>
       <c r="J8">
-        <v>243.0225131564699</v>
+        <v>243.77015980174409</v>
       </c>
       <c r="K8">
-        <v>252.39191656463419</v>
+        <v>252.01002005873261</v>
       </c>
       <c r="L8">
-        <v>266.3330745634708</v>
+        <v>266.07326855811522</v>
       </c>
       <c r="M8">
-        <v>277.57040226546991</v>
+        <v>277.62183320380592</v>
       </c>
       <c r="N8">
-        <v>276.54711862212542</v>
+        <v>277.45421976589381</v>
       </c>
       <c r="O8">
-        <v>269.16467950512799</v>
+        <v>270.12846724301659</v>
       </c>
       <c r="P8">
-        <v>262.32880737643109</v>
+        <v>263.77566950792391</v>
       </c>
       <c r="Q8">
-        <v>266.48345150131058</v>
+        <v>268.02803899113923</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1094,52 +1014,52 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>263.6792948789178</v>
+        <v>261.33549674174492</v>
       </c>
       <c r="C9">
-        <v>272.88724468067659</v>
+        <v>272.71912740974091</v>
       </c>
       <c r="D9">
-        <v>257.92665656903762</v>
+        <v>257.20852384939258</v>
       </c>
       <c r="E9">
-        <v>245.42691002101159</v>
+        <v>243.97296513394471</v>
       </c>
       <c r="F9">
-        <v>243.91587190493269</v>
+        <v>242.39493764228069</v>
       </c>
       <c r="G9">
-        <v>243.3218122777059</v>
+        <v>241.90119322547599</v>
       </c>
       <c r="H9">
-        <v>244.25029972078909</v>
+        <v>243.18072690003669</v>
       </c>
       <c r="I9">
-        <v>240.8272654190051</v>
+        <v>239.62664046456121</v>
       </c>
       <c r="J9">
-        <v>244.20035907746919</v>
+        <v>243.67053427252</v>
       </c>
       <c r="K9">
-        <v>248.91160221038669</v>
+        <v>247.50624762108581</v>
       </c>
       <c r="L9">
-        <v>257.32356360045418</v>
+        <v>255.71085499719041</v>
       </c>
       <c r="M9">
-        <v>269.76645052310448</v>
+        <v>266.95452412206322</v>
       </c>
       <c r="N9">
-        <v>269.68419929077601</v>
+        <v>267.13062839694089</v>
       </c>
       <c r="O9">
-        <v>260.07252674669331</v>
+        <v>258.81487205114001</v>
       </c>
       <c r="P9">
-        <v>251.54361581172449</v>
+        <v>251.2418640273502</v>
       </c>
       <c r="Q9">
-        <v>257.10707666739671</v>
+        <v>256.08341761141583</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1147,52 +1067,52 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>266.42993402466402</v>
+        <v>264.50253039006247</v>
       </c>
       <c r="C10">
-        <v>273.3329907560543</v>
+        <v>273.94423099576642</v>
       </c>
       <c r="D10">
-        <v>258.02964100171152</v>
+        <v>259.60090304937881</v>
       </c>
       <c r="E10">
-        <v>245.64862907177249</v>
+        <v>246.18346836760369</v>
       </c>
       <c r="F10">
-        <v>244.06784779410199</v>
+        <v>245.1632665298215</v>
       </c>
       <c r="G10">
-        <v>243.57174482490589</v>
+        <v>244.67073541975449</v>
       </c>
       <c r="H10">
-        <v>244.8477181349036</v>
+        <v>245.49597779900219</v>
       </c>
       <c r="I10">
-        <v>241.52937350135679</v>
+        <v>241.61866822395851</v>
       </c>
       <c r="J10">
-        <v>243.98261368454061</v>
+        <v>244.91225098649321</v>
       </c>
       <c r="K10">
-        <v>249.1800502544271</v>
+        <v>249.23641444805011</v>
       </c>
       <c r="L10">
-        <v>255.7868048069144</v>
+        <v>256.11498430127102</v>
       </c>
       <c r="M10">
-        <v>268.23907942266959</v>
+        <v>267.37864363792318</v>
       </c>
       <c r="N10">
-        <v>268.23499235764717</v>
+        <v>267.78388237686443</v>
       </c>
       <c r="O10">
-        <v>259.64929806478648</v>
+        <v>260.46898185872237</v>
       </c>
       <c r="P10">
-        <v>251.27880456200819</v>
+        <v>252.1727773113916</v>
       </c>
       <c r="Q10">
-        <v>256.39761719435751</v>
+        <v>256.92132353703113</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1200,52 +1120,52 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>264.61989711743018</v>
+        <v>262.81850500538081</v>
       </c>
       <c r="C11">
-        <v>272.84596660447102</v>
+        <v>272.29577688535818</v>
       </c>
       <c r="D11">
-        <v>257.85875368071561</v>
+        <v>256.75520431968778</v>
       </c>
       <c r="E11">
-        <v>244.596296853019</v>
+        <v>243.51206882948199</v>
       </c>
       <c r="F11">
-        <v>242.83957630792551</v>
+        <v>241.56647897275991</v>
       </c>
       <c r="G11">
-        <v>242.33001305709089</v>
+        <v>241.0353216829505</v>
       </c>
       <c r="H11">
-        <v>242.9138249746878</v>
+        <v>241.70289745348381</v>
       </c>
       <c r="I11">
-        <v>239.42409777021379</v>
+        <v>238.3811127313233</v>
       </c>
       <c r="J11">
-        <v>242.66407886583249</v>
+        <v>241.53599241799569</v>
       </c>
       <c r="K11">
-        <v>247.22899983743051</v>
+        <v>246.02840353944029</v>
       </c>
       <c r="L11">
-        <v>256.15331606398541</v>
+        <v>255.14592855979879</v>
       </c>
       <c r="M11">
-        <v>269.27984644907929</v>
+        <v>268.90639059933</v>
       </c>
       <c r="N11">
-        <v>268.89684865488488</v>
+        <v>269.84889047924872</v>
       </c>
       <c r="O11">
-        <v>259.80884122318582</v>
+        <v>260.95372763845421</v>
       </c>
       <c r="P11">
-        <v>251.7570514830384</v>
+        <v>252.4088813810184</v>
       </c>
       <c r="Q11">
-        <v>253.1772251515082</v>
+        <v>254.83943148453929</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1253,52 +1173,52 @@
         <v>27</v>
       </c>
       <c r="B12">
-        <v>252.76900437835221</v>
+        <v>252.62724044445869</v>
       </c>
       <c r="C12">
-        <v>250.98464170616381</v>
+        <v>251.19622354899499</v>
       </c>
       <c r="D12">
-        <v>248.23282865703439</v>
+        <v>248.6246429529636</v>
       </c>
       <c r="E12">
-        <v>241.54314053435391</v>
+        <v>241.77054614406521</v>
       </c>
       <c r="F12">
-        <v>235.94121493546831</v>
+        <v>235.41559389663971</v>
       </c>
       <c r="G12">
-        <v>234.9645817414937</v>
+        <v>234.48194607158351</v>
       </c>
       <c r="H12">
-        <v>234.89393124537989</v>
+        <v>234.66642706208731</v>
       </c>
       <c r="I12">
-        <v>236.81048382359251</v>
+        <v>235.95441612348421</v>
       </c>
       <c r="J12">
-        <v>242.57373682662671</v>
+        <v>242.25827790673361</v>
       </c>
       <c r="K12">
-        <v>251.93512255927519</v>
+        <v>252.04316731598311</v>
       </c>
       <c r="L12">
-        <v>264.31217081894829</v>
+        <v>264.31712783220968</v>
       </c>
       <c r="M12">
-        <v>276.20427386407118</v>
+        <v>276.36357612128938</v>
       </c>
       <c r="N12">
-        <v>283.13693645615621</v>
+        <v>284.41390848817713</v>
       </c>
       <c r="O12">
-        <v>280.70294727386931</v>
+        <v>281.82827005003242</v>
       </c>
       <c r="P12">
-        <v>278.67528430427251</v>
+        <v>278.69948047890477</v>
       </c>
       <c r="Q12">
-        <v>279.5658408592468</v>
+        <v>280.85327543907698</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1306,52 +1226,52 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>252.13653486192709</v>
+        <v>253.33009441520011</v>
       </c>
       <c r="C13">
-        <v>251.07393070241531</v>
+        <v>251.0236952765959</v>
       </c>
       <c r="D13">
-        <v>248.33809198400931</v>
+        <v>248.24179530088759</v>
       </c>
       <c r="E13">
-        <v>245.50263329340021</v>
+        <v>245.90864081013919</v>
       </c>
       <c r="F13">
-        <v>242.63041548477901</v>
+        <v>243.09431772526551</v>
       </c>
       <c r="G13">
-        <v>240.87515722026259</v>
+        <v>240.82610024420731</v>
       </c>
       <c r="H13">
-        <v>243.31595549524039</v>
+        <v>242.80628979345161</v>
       </c>
       <c r="I13">
-        <v>244.70838701392859</v>
+        <v>243.90496235150599</v>
       </c>
       <c r="J13">
-        <v>251.32657805780269</v>
+        <v>250.80692957806889</v>
       </c>
       <c r="K13">
-        <v>257.2477689974495</v>
+        <v>257.08496052072007</v>
       </c>
       <c r="L13">
-        <v>270.07559783551369</v>
+        <v>270.43343025238261</v>
       </c>
       <c r="M13">
-        <v>275.41520900430368</v>
+        <v>276.37549352961781</v>
       </c>
       <c r="N13">
-        <v>278.92874414522288</v>
+        <v>280.56452018454308</v>
       </c>
       <c r="O13">
-        <v>283.84218212344342</v>
+        <v>286.41650834869068</v>
       </c>
       <c r="P13">
-        <v>290.42583864415019</v>
+        <v>292.79004430961697</v>
       </c>
       <c r="Q13">
-        <v>299.48283970666989</v>
+        <v>304.25087088864609</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1359,52 +1279,52 @@
         <v>29</v>
       </c>
       <c r="B14">
-        <v>248.12752320368679</v>
+        <v>247.92693573354779</v>
       </c>
       <c r="C14">
-        <v>284.29994283420592</v>
+        <v>283.9133271984312</v>
       </c>
       <c r="D14">
-        <v>253.90738858304749</v>
+        <v>253.22939757322069</v>
       </c>
       <c r="E14">
-        <v>239.68420949191611</v>
+        <v>238.17543688579869</v>
       </c>
       <c r="F14">
-        <v>229.86533054300691</v>
+        <v>228.8717077530373</v>
       </c>
       <c r="G14">
-        <v>228.42795023671809</v>
+        <v>227.1478643727792</v>
       </c>
       <c r="H14">
-        <v>229.43875646458761</v>
+        <v>227.30916256187871</v>
       </c>
       <c r="I14">
-        <v>231.52331902422961</v>
+        <v>230.24226040284941</v>
       </c>
       <c r="J14">
-        <v>230.13162539578741</v>
+        <v>228.87587124734321</v>
       </c>
       <c r="K14">
-        <v>237.77608925208361</v>
+        <v>235.34788900105511</v>
       </c>
       <c r="L14">
-        <v>247.23438193462081</v>
+        <v>245.79571736898171</v>
       </c>
       <c r="M14">
-        <v>250.80852093856859</v>
+        <v>248.99386067799091</v>
       </c>
       <c r="N14">
-        <v>258.47882818241078</v>
+        <v>257.42397141128021</v>
       </c>
       <c r="O14">
-        <v>259.19942409322692</v>
+        <v>259.67827276090918</v>
       </c>
       <c r="P14">
-        <v>255.23960031075131</v>
+        <v>256.20095985524478</v>
       </c>
       <c r="Q14">
-        <v>248.93336341125371</v>
+        <v>248.93981887181269</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1412,52 +1332,52 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>250.08578485820411</v>
+        <v>249.86446424210681</v>
       </c>
       <c r="C15">
-        <v>284.76263076556768</v>
+        <v>283.99708929828682</v>
       </c>
       <c r="D15">
-        <v>254.4243492982751</v>
+        <v>253.37649583562521</v>
       </c>
       <c r="E15">
-        <v>239.61775598750151</v>
+        <v>238.27894144238391</v>
       </c>
       <c r="F15">
-        <v>229.41581411996901</v>
+        <v>229.34999005367061</v>
       </c>
       <c r="G15">
-        <v>227.91258477895681</v>
+        <v>227.47914763436449</v>
       </c>
       <c r="H15">
-        <v>228.6559614769387</v>
+        <v>228.1158155754452</v>
       </c>
       <c r="I15">
-        <v>231.08236397508401</v>
+        <v>230.05681868998309</v>
       </c>
       <c r="J15">
-        <v>230.13312729155359</v>
+        <v>229.10557830958641</v>
       </c>
       <c r="K15">
-        <v>237.08416932040939</v>
+        <v>235.29760898347749</v>
       </c>
       <c r="L15">
-        <v>247.5160036640352</v>
+        <v>245.27400417042591</v>
       </c>
       <c r="M15">
-        <v>250.8951255961787</v>
+        <v>246.68466291586981</v>
       </c>
       <c r="N15">
-        <v>259.43065480709947</v>
+        <v>255.34556875090539</v>
       </c>
       <c r="O15">
-        <v>260.32327504242772</v>
+        <v>256.41280680988888</v>
       </c>
       <c r="P15">
-        <v>256.53670406189008</v>
+        <v>253.208518201641</v>
       </c>
       <c r="Q15">
-        <v>250.6570226830022</v>
+        <v>246.6219369453832</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1465,52 +1385,52 @@
         <v>31</v>
       </c>
       <c r="B16">
-        <v>248.67463762580161</v>
+        <v>250.5434361672846</v>
       </c>
       <c r="C16">
-        <v>284.04821287825507</v>
+        <v>283.58940070408403</v>
       </c>
       <c r="D16">
-        <v>253.2949214451063</v>
+        <v>253.06392308509101</v>
       </c>
       <c r="E16">
-        <v>237.74096540253359</v>
+        <v>237.74040333986889</v>
       </c>
       <c r="F16">
-        <v>228.5697613505269</v>
+        <v>228.2220376676633</v>
       </c>
       <c r="G16">
-        <v>226.82502594992229</v>
+        <v>226.24173030868349</v>
       </c>
       <c r="H16">
-        <v>227.41241212582801</v>
+        <v>227.5544692305991</v>
       </c>
       <c r="I16">
-        <v>230.31146899122029</v>
+        <v>229.2529998366048</v>
       </c>
       <c r="J16">
-        <v>229.12259935368289</v>
+        <v>228.62418741137759</v>
       </c>
       <c r="K16">
-        <v>235.89845023317261</v>
+        <v>234.95602891471529</v>
       </c>
       <c r="L16">
-        <v>246.31671822839601</v>
+        <v>245.00109058672601</v>
       </c>
       <c r="M16">
-        <v>248.76623269216839</v>
+        <v>246.95293578212281</v>
       </c>
       <c r="N16">
-        <v>256.51319001605822</v>
+        <v>254.08914544074261</v>
       </c>
       <c r="O16">
-        <v>260.14605411123011</v>
+        <v>256.36537428357792</v>
       </c>
       <c r="P16">
-        <v>256.2252302649859</v>
+        <v>254.5934191966698</v>
       </c>
       <c r="Q16">
-        <v>250.01025219035341</v>
+        <v>249.27020117416831</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1518,52 +1438,52 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>249.87090508446701</v>
+        <v>248.43388523282849</v>
       </c>
       <c r="C17">
-        <v>283.7334701469149</v>
+        <v>284.35175500786079</v>
       </c>
       <c r="D17">
-        <v>253.3733923028106</v>
+        <v>253.53096702250181</v>
       </c>
       <c r="E17">
-        <v>238.79055342369449</v>
+        <v>238.62347130098681</v>
       </c>
       <c r="F17">
-        <v>229.42514859378929</v>
+        <v>228.75346868262091</v>
       </c>
       <c r="G17">
-        <v>228.17741557229559</v>
+        <v>226.79317974818079</v>
       </c>
       <c r="H17">
-        <v>228.82981498491969</v>
+        <v>227.62526751584551</v>
       </c>
       <c r="I17">
-        <v>231.63736979388091</v>
+        <v>229.9131907617022</v>
       </c>
       <c r="J17">
-        <v>230.1436151469828</v>
+        <v>228.51636524797561</v>
       </c>
       <c r="K17">
-        <v>237.03084567210951</v>
+        <v>235.14751284591799</v>
       </c>
       <c r="L17">
-        <v>246.84729119755011</v>
+        <v>244.7466471863813</v>
       </c>
       <c r="M17">
-        <v>249.28979880632809</v>
+        <v>246.75269076057589</v>
       </c>
       <c r="N17">
-        <v>256.57025272648468</v>
+        <v>251.287711861964</v>
       </c>
       <c r="O17">
-        <v>258.51844584019562</v>
+        <v>252.876840869695</v>
       </c>
       <c r="P17">
-        <v>254.15187382360671</v>
+        <v>248.15202506327239</v>
       </c>
       <c r="Q17">
-        <v>249.1517617043354</v>
+        <v>244.50510836489499</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1571,52 +1491,52 @@
         <v>33</v>
       </c>
       <c r="B18">
-        <v>252.41644524173441</v>
+        <v>252.94659522604559</v>
       </c>
       <c r="C18">
-        <v>250.26702825825211</v>
+        <v>250.5020136596651</v>
       </c>
       <c r="D18">
-        <v>248.89148587892981</v>
+        <v>248.42061297377339</v>
       </c>
       <c r="E18">
-        <v>243.28933924434219</v>
+        <v>242.3661285631965</v>
       </c>
       <c r="F18">
-        <v>236.49870465025941</v>
+        <v>235.78101835779799</v>
       </c>
       <c r="G18">
-        <v>234.15571937098929</v>
+        <v>233.02227724630129</v>
       </c>
       <c r="H18">
-        <v>234.94474831061049</v>
+        <v>233.9869412425324</v>
       </c>
       <c r="I18">
-        <v>236.06469205462821</v>
+        <v>234.90567758062079</v>
       </c>
       <c r="J18">
-        <v>246.8239243876416</v>
+        <v>245.72374896318959</v>
       </c>
       <c r="K18">
-        <v>249.26424583282261</v>
+        <v>248.5954969114311</v>
       </c>
       <c r="L18">
-        <v>259.5218156354108</v>
+        <v>259.8128172601912</v>
       </c>
       <c r="M18">
-        <v>266.13997644271188</v>
+        <v>266.13552775474972</v>
       </c>
       <c r="N18">
-        <v>268.43948369938153</v>
+        <v>268.43629687939472</v>
       </c>
       <c r="O18">
-        <v>263.35332860074692</v>
+        <v>263.45091492653057</v>
       </c>
       <c r="P18">
-        <v>260.84332275132158</v>
+        <v>261.03397939225829</v>
       </c>
       <c r="Q18">
-        <v>259.62156079255487</v>
+        <v>258.53555074547808</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1624,52 +1544,52 @@
         <v>34</v>
       </c>
       <c r="B19">
-        <v>251.54700371863041</v>
+        <v>254.02883845152579</v>
       </c>
       <c r="C19">
-        <v>249.77274097129279</v>
+        <v>250.37002774756959</v>
       </c>
       <c r="D19">
-        <v>248.23286994397731</v>
+        <v>249.23694301963349</v>
       </c>
       <c r="E19">
-        <v>244.6196085870522</v>
+        <v>245.5654979922561</v>
       </c>
       <c r="F19">
-        <v>239.3909081635272</v>
+        <v>240.89353976766151</v>
       </c>
       <c r="G19">
-        <v>232.077769142731</v>
+        <v>233.79559792559851</v>
       </c>
       <c r="H19">
-        <v>233.94645412907431</v>
+        <v>236.49141774637479</v>
       </c>
       <c r="I19">
-        <v>236.14058995839491</v>
+        <v>239.6983515681633</v>
       </c>
       <c r="J19">
-        <v>243.70970503675639</v>
+        <v>247.71041550974439</v>
       </c>
       <c r="K19">
-        <v>256.38758623723851</v>
+        <v>260.29560916798442</v>
       </c>
       <c r="L19">
-        <v>262.15102239389432</v>
+        <v>265.97701907367377</v>
       </c>
       <c r="M19">
-        <v>267.24669259076052</v>
+        <v>270.71544657633302</v>
       </c>
       <c r="N19">
-        <v>264.90431542353508</v>
+        <v>268.15815485230638</v>
       </c>
       <c r="O19">
-        <v>263.97050584876462</v>
+        <v>266.40142851715342</v>
       </c>
       <c r="P19">
-        <v>260.8993151645717</v>
+        <v>263.29306620787162</v>
       </c>
       <c r="Q19">
-        <v>263.93993279102648</v>
+        <v>267.07039840790122</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1677,52 +1597,52 @@
         <v>35</v>
       </c>
       <c r="B20">
-        <v>252.24063909666859</v>
+        <v>254.37271183446401</v>
       </c>
       <c r="C20">
-        <v>249.0711413788969</v>
+        <v>249.84084111839039</v>
       </c>
       <c r="D20">
-        <v>247.10751882940781</v>
+        <v>248.90901824302961</v>
       </c>
       <c r="E20">
-        <v>240.9062028608061</v>
+        <v>243.42679499881439</v>
       </c>
       <c r="F20">
-        <v>236.4809580539436</v>
+        <v>239.38655610452861</v>
       </c>
       <c r="G20">
-        <v>233.36519209490609</v>
+        <v>235.72670714443939</v>
       </c>
       <c r="H20">
-        <v>233.10008385943351</v>
+        <v>234.70691078302221</v>
       </c>
       <c r="I20">
-        <v>239.08201013061191</v>
+        <v>240.67834815710319</v>
       </c>
       <c r="J20">
-        <v>244.14264478446501</v>
+        <v>246.37271757337331</v>
       </c>
       <c r="K20">
-        <v>257.51589763888489</v>
+        <v>259.21089190717441</v>
       </c>
       <c r="L20">
-        <v>266.28519241477511</v>
+        <v>266.74957014286582</v>
       </c>
       <c r="M20">
-        <v>263.46716873498832</v>
+        <v>263.67565509767741</v>
       </c>
       <c r="N20">
-        <v>258.30354849776842</v>
+        <v>257.11973548387152</v>
       </c>
       <c r="O20">
-        <v>259.04950879939508</v>
+        <v>257.14002387411648</v>
       </c>
       <c r="P20">
-        <v>251.0891483907173</v>
+        <v>249.10079192238379</v>
       </c>
       <c r="Q20">
-        <v>255.90060224572019</v>
+        <v>254.55856596154931</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1730,52 +1650,52 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>260.39166289378738</v>
+        <v>260.78041071919711</v>
       </c>
       <c r="C21">
-        <v>265.0457487485628</v>
+        <v>265.58449338177991</v>
       </c>
       <c r="D21">
-        <v>251.33929372332901</v>
+        <v>251.2811328622997</v>
       </c>
       <c r="E21">
-        <v>251.49415781463401</v>
+        <v>250.70020794551101</v>
       </c>
       <c r="F21">
-        <v>247.48996331135021</v>
+        <v>245.63149188662851</v>
       </c>
       <c r="G21">
-        <v>243.89904796479419</v>
+        <v>241.81105310764281</v>
       </c>
       <c r="H21">
-        <v>243.3334595184734</v>
+        <v>241.99985870426619</v>
       </c>
       <c r="I21">
-        <v>260.99965358842928</v>
+        <v>258.09182781236899</v>
       </c>
       <c r="J21">
-        <v>268.31205563817508</v>
+        <v>266.06222382033133</v>
       </c>
       <c r="K21">
-        <v>269.95216756367603</v>
+        <v>270.0232479645021</v>
       </c>
       <c r="L21">
-        <v>278.52005185051172</v>
+        <v>278.06269541429202</v>
       </c>
       <c r="M21">
-        <v>285.07429997049769</v>
+        <v>284.65254424935029</v>
       </c>
       <c r="N21">
-        <v>298.51786825575311</v>
+        <v>297.20721887881808</v>
       </c>
       <c r="O21">
-        <v>309.78640911913169</v>
+        <v>308.23279815023261</v>
       </c>
       <c r="P21">
-        <v>322.56845278665941</v>
+        <v>321.41820783268611</v>
       </c>
       <c r="Q21">
-        <v>343.50688321652223</v>
+        <v>341.76351328991421</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1783,52 +1703,52 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>260.46175136884938</v>
+        <v>259.11157354145018</v>
       </c>
       <c r="C22">
-        <v>265.45060090831981</v>
+        <v>265.09584404158011</v>
       </c>
       <c r="D22">
-        <v>251.59153173468869</v>
+        <v>251.2281184816911</v>
       </c>
       <c r="E22">
-        <v>251.6430174803516</v>
+        <v>251.46499525975</v>
       </c>
       <c r="F22">
-        <v>246.59605291478741</v>
+        <v>246.9758632866893</v>
       </c>
       <c r="G22">
-        <v>242.5739815178612</v>
+        <v>243.28712248137231</v>
       </c>
       <c r="H22">
-        <v>238.5011677397834</v>
+        <v>239.41810599573151</v>
       </c>
       <c r="I22">
-        <v>255.7584832324863</v>
+        <v>258.00133014748599</v>
       </c>
       <c r="J22">
-        <v>262.44879389227492</v>
+        <v>264.54769262954773</v>
       </c>
       <c r="K22">
-        <v>265.02843223362459</v>
+        <v>266.93568859557621</v>
       </c>
       <c r="L22">
-        <v>271.58089663266418</v>
+        <v>271.85200043165253</v>
       </c>
       <c r="M22">
-        <v>280.95317977299328</v>
+        <v>281.94970856487981</v>
       </c>
       <c r="N22">
-        <v>293.86286868419512</v>
+        <v>294.5253640628469</v>
       </c>
       <c r="O22">
-        <v>300.81009964509809</v>
+        <v>302.35354874291511</v>
       </c>
       <c r="P22">
-        <v>315.92409085526378</v>
+        <v>317.61288193587188</v>
       </c>
       <c r="Q22">
-        <v>334.72059891459998</v>
+        <v>337.11919253940209</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1836,52 +1756,52 @@
         <v>38</v>
       </c>
       <c r="B23">
-        <v>252.69354786212659</v>
+        <v>252.5721922732115</v>
       </c>
       <c r="C23">
-        <v>251.71180539916699</v>
+        <v>251.7475476438116</v>
       </c>
       <c r="D23">
-        <v>251.5964894447614</v>
+        <v>251.65564133921319</v>
       </c>
       <c r="E23">
-        <v>243.4088574296909</v>
+        <v>242.83215340036551</v>
       </c>
       <c r="F23">
-        <v>239.76428093540511</v>
+        <v>239.6597229607577</v>
       </c>
       <c r="G23">
-        <v>249.1849875010669</v>
+        <v>248.9155958579143</v>
       </c>
       <c r="H23">
-        <v>274.47069638123321</v>
+        <v>274.21368937143438</v>
       </c>
       <c r="I23">
-        <v>286.02688692833129</v>
+        <v>285.69788782185202</v>
       </c>
       <c r="J23">
-        <v>288.54822550395107</v>
+        <v>288.5945521770073</v>
       </c>
       <c r="K23">
-        <v>298.113647651934</v>
+        <v>297.98306640674832</v>
       </c>
       <c r="L23">
-        <v>308.91049915429699</v>
+        <v>307.86622566805318</v>
       </c>
       <c r="M23">
-        <v>322.07849578851437</v>
+        <v>321.11591992971597</v>
       </c>
       <c r="N23">
-        <v>338.34209643986088</v>
+        <v>338.88795604641098</v>
       </c>
       <c r="O23">
-        <v>353.51588940257272</v>
+        <v>353.23115392892947</v>
       </c>
       <c r="P23">
-        <v>365.00267083350269</v>
+        <v>364.93578123638531</v>
       </c>
       <c r="Q23">
-        <v>386.56154782322392</v>
+        <v>385.96531326057112</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -1889,52 +1809,52 @@
         <v>39</v>
       </c>
       <c r="B24">
-        <v>329.17234956996981</v>
+        <v>328.08135792217962</v>
       </c>
       <c r="C24">
-        <v>329.17234956996981</v>
+        <v>328.08135792217962</v>
       </c>
       <c r="D24">
-        <v>334.07259259181308</v>
+        <v>332.42151527907902</v>
       </c>
       <c r="E24">
-        <v>324.76143784232028</v>
+        <v>325.21054902321077</v>
       </c>
       <c r="F24">
-        <v>340.54493983330889</v>
+        <v>340.76933072668089</v>
       </c>
       <c r="G24">
-        <v>365.67961764185571</v>
+        <v>364.42499706968027</v>
       </c>
       <c r="H24">
-        <v>366.96684617462631</v>
+        <v>365.95755822316488</v>
       </c>
       <c r="I24">
-        <v>374.72886755987832</v>
+        <v>372.66745629723852</v>
       </c>
       <c r="J24">
-        <v>388.77577953866398</v>
+        <v>386.652905068726</v>
       </c>
       <c r="K24">
-        <v>400.97223953435127</v>
+        <v>397.32526553667611</v>
       </c>
       <c r="L24">
-        <v>402.88172102806402</v>
+        <v>400.05712905005521</v>
       </c>
       <c r="M24">
-        <v>411.17834069490198</v>
+        <v>407.6576753608291</v>
       </c>
       <c r="N24">
-        <v>414.08556194184501</v>
+        <v>411.48840657311843</v>
       </c>
       <c r="O24">
-        <v>434.41992844425027</v>
+        <v>430.16359459915719</v>
       </c>
       <c r="P24">
-        <v>443.25475789151972</v>
+        <v>436.91163444154222</v>
       </c>
       <c r="Q24">
-        <v>451.26641919235448</v>
+        <v>443.77129563084827</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1942,52 +1862,52 @@
         <v>40</v>
       </c>
       <c r="B25">
-        <v>335.11805605945352</v>
+        <v>335.19200334199678</v>
       </c>
       <c r="C25">
-        <v>335.11805605945352</v>
+        <v>335.19200334199678</v>
       </c>
       <c r="D25">
-        <v>339.38805404649003</v>
+        <v>337.91305738080882</v>
       </c>
       <c r="E25">
-        <v>343.51928413869888</v>
+        <v>341.42748139699438</v>
       </c>
       <c r="F25">
-        <v>346.79568364604648</v>
+        <v>344.67615166311077</v>
       </c>
       <c r="G25">
-        <v>353.80391735799873</v>
+        <v>353.52517375400521</v>
       </c>
       <c r="H25">
-        <v>377.00963994369602</v>
+        <v>376.16364555119702</v>
       </c>
       <c r="I25">
-        <v>384.96780083943952</v>
+        <v>384.51244603570132</v>
       </c>
       <c r="J25">
-        <v>395.58879075555711</v>
+        <v>395.74655488612052</v>
       </c>
       <c r="K25">
-        <v>402.85064306857021</v>
+        <v>402.7142019350124</v>
       </c>
       <c r="L25">
-        <v>413.668917423371</v>
+        <v>412.96805167960912</v>
       </c>
       <c r="M25">
-        <v>425.0401162149268</v>
+        <v>425.23232548513192</v>
       </c>
       <c r="N25">
-        <v>435.91204916423402</v>
+        <v>436.62878458186168</v>
       </c>
       <c r="O25">
-        <v>445.74436796303581</v>
+        <v>447.32060402959331</v>
       </c>
       <c r="P25">
-        <v>453.24220995901419</v>
+        <v>455.47607461934649</v>
       </c>
       <c r="Q25">
-        <v>457.60732799793379</v>
+        <v>460.07380286608122</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1995,52 +1915,52 @@
         <v>41</v>
       </c>
       <c r="B26">
-        <v>334.98457810422161</v>
+        <v>335.75273989498248</v>
       </c>
       <c r="C26">
-        <v>334.98457810422161</v>
+        <v>335.10640431527702</v>
       </c>
       <c r="D26">
-        <v>337.64073676520059</v>
+        <v>336.91859989559208</v>
       </c>
       <c r="E26">
-        <v>335.13252329582082</v>
+        <v>334.25925671375239</v>
       </c>
       <c r="F26">
-        <v>335.61955596636489</v>
+        <v>334.34110060246343</v>
       </c>
       <c r="G26">
-        <v>347.14557951465309</v>
+        <v>345.14956871707381</v>
       </c>
       <c r="H26">
-        <v>354.6226411796178</v>
+        <v>352.82528503397089</v>
       </c>
       <c r="I26">
-        <v>373.53795975601332</v>
+        <v>371.81695627258011</v>
       </c>
       <c r="J26">
-        <v>378.34602638410149</v>
+        <v>377.47641943155759</v>
       </c>
       <c r="K26">
-        <v>370.70046407200039</v>
+        <v>369.41628749196991</v>
       </c>
       <c r="L26">
-        <v>367.42771076047472</v>
+        <v>367.0843608449581</v>
       </c>
       <c r="M26">
-        <v>375.71860471980949</v>
+        <v>373.92193052998869</v>
       </c>
       <c r="N26">
-        <v>405.19713972308131</v>
+        <v>406.95702476146391</v>
       </c>
       <c r="O26">
-        <v>398.10718818917587</v>
+        <v>397.91011410413307</v>
       </c>
       <c r="P26">
-        <v>394.22875023253272</v>
+        <v>396.08259006371787</v>
       </c>
       <c r="Q26">
-        <v>395.80110283590818</v>
+        <v>394.37011683177951</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -2048,52 +1968,52 @@
         <v>42</v>
       </c>
       <c r="B27">
-        <v>340.76805009074218</v>
+        <v>342.22628639930548</v>
       </c>
       <c r="C27">
-        <v>339.75534441690672</v>
+        <v>340.76378236997471</v>
       </c>
       <c r="D27">
-        <v>343.71719530208452</v>
+        <v>343.82145613748878</v>
       </c>
       <c r="E27">
-        <v>348.11814704734059</v>
+        <v>346.98761374083762</v>
       </c>
       <c r="F27">
-        <v>335.46248421721651</v>
+        <v>335.9983292593663</v>
       </c>
       <c r="G27">
-        <v>350.24380032500699</v>
+        <v>349.37054013023851</v>
       </c>
       <c r="H27">
-        <v>356.09075583035201</v>
+        <v>354.32187069670522</v>
       </c>
       <c r="I27">
-        <v>345.97260447750148</v>
+        <v>344.36707193660078</v>
       </c>
       <c r="J27">
-        <v>360.23169793191153</v>
+        <v>358.17040853841172</v>
       </c>
       <c r="K27">
-        <v>369.05494491683822</v>
+        <v>365.48693339310501</v>
       </c>
       <c r="L27">
-        <v>378.70654454930087</v>
+        <v>375.69438417510997</v>
       </c>
       <c r="M27">
-        <v>394.42207436851407</v>
+        <v>389.86447633201419</v>
       </c>
       <c r="N27">
-        <v>401.27230122603981</v>
+        <v>398.77302995785573</v>
       </c>
       <c r="O27">
-        <v>384.20807219176692</v>
+        <v>382.21222220462312</v>
       </c>
       <c r="P27">
-        <v>394.30597625558579</v>
+        <v>392.83127694926912</v>
       </c>
       <c r="Q27">
-        <v>397.99495494120538</v>
+        <v>397.52990845769261</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -2101,52 +2021,52 @@
         <v>43</v>
       </c>
       <c r="B28">
-        <v>221.0192589021778</v>
+        <v>221.19622020976541</v>
       </c>
       <c r="C28">
-        <v>237.94298400557969</v>
-      </c>
-      <c r="D28">
-        <v>221.33206709531021</v>
+        <v>237.4354597557917</v>
+      </c>
+      <c r="D28" s="2">
+        <v>220.69295300211891</v>
       </c>
       <c r="E28">
-        <v>212.2531688711357</v>
+        <v>211.73139939565931</v>
       </c>
       <c r="F28">
-        <v>205.8700113439717</v>
+        <v>204.8102406406733</v>
       </c>
       <c r="G28">
-        <v>205.9533636151059</v>
+        <v>204.53590407411789</v>
       </c>
       <c r="H28">
-        <v>204.13818773866461</v>
+        <v>203.06917872192969</v>
       </c>
       <c r="I28">
-        <v>204.99176867962441</v>
+        <v>204.4940908785037</v>
       </c>
       <c r="J28">
-        <v>207.4276844694854</v>
+        <v>206.93294170606191</v>
       </c>
       <c r="K28">
-        <v>215.5995576711278</v>
+        <v>214.3400666993403</v>
       </c>
       <c r="L28">
-        <v>226.83704305068471</v>
+        <v>224.3226039017305</v>
       </c>
       <c r="M28">
-        <v>234.36600719266471</v>
+        <v>232.19093487584399</v>
       </c>
       <c r="N28">
-        <v>249.6485244226082</v>
+        <v>246.96473457502699</v>
       </c>
       <c r="O28">
-        <v>264.74508851664473</v>
+        <v>262.35855626574471</v>
       </c>
       <c r="P28">
-        <v>281.65590291889868</v>
+        <v>279.50120626735122</v>
       </c>
       <c r="Q28">
-        <v>300.91078463589548</v>
+        <v>298.32149046836912</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -2154,52 +2074,52 @@
         <v>44</v>
       </c>
       <c r="B29">
-        <v>207.05933972089721</v>
+        <v>208.13557063434311</v>
       </c>
       <c r="C29">
-        <v>238.1220349649243</v>
-      </c>
-      <c r="D29">
-        <v>220.36619028593589</v>
-      </c>
-      <c r="E29">
-        <v>207.6794001305804</v>
-      </c>
-      <c r="F29">
-        <v>196.39151829797939</v>
+        <v>239.02746695571051</v>
+      </c>
+      <c r="D29" s="3">
+        <v>220.92512435203011</v>
+      </c>
+      <c r="E29" s="2">
+        <v>207.96859624040499</v>
+      </c>
+      <c r="F29" s="2">
+        <v>197.56919155900081</v>
       </c>
       <c r="G29">
-        <v>192.01294849327829</v>
+        <v>192.43921578667451</v>
       </c>
       <c r="H29">
-        <v>188.80046084090841</v>
+        <v>189.53204918765721</v>
       </c>
       <c r="I29">
-        <v>190.87916493931581</v>
+        <v>190.978374869795</v>
       </c>
       <c r="J29">
-        <v>200.07643027247391</v>
+        <v>201.76728862150429</v>
       </c>
       <c r="K29">
-        <v>199.67756333307659</v>
+        <v>201.9278086620287</v>
       </c>
       <c r="L29">
-        <v>200.48656501967281</v>
+        <v>201.96447872283781</v>
       </c>
       <c r="M29">
-        <v>212.78926515703671</v>
+        <v>214.24357113284671</v>
       </c>
       <c r="N29">
-        <v>221.08093895691849</v>
+        <v>222.31166065474719</v>
       </c>
       <c r="O29">
-        <v>237.1834998564816</v>
+        <v>238.34670065422199</v>
       </c>
       <c r="P29">
-        <v>247.87786053007119</v>
+        <v>248.8659517128489</v>
       </c>
       <c r="Q29">
-        <v>272.51676204772622</v>
+        <v>273.57848250407199</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -2207,52 +2127,52 @@
         <v>45</v>
       </c>
       <c r="B30">
-        <v>217.8694235551684</v>
+        <v>217.952361907511</v>
       </c>
       <c r="C30">
-        <v>234.660869472993</v>
+        <v>234.75060391527131</v>
       </c>
       <c r="D30">
-        <v>226.32896281399209</v>
-      </c>
-      <c r="E30">
-        <v>213.43919220741469</v>
+        <v>225.97601482979661</v>
+      </c>
+      <c r="E30" s="2">
+        <v>212.24846694227</v>
       </c>
       <c r="F30">
-        <v>203.7430234699477</v>
+        <v>202.64352834334201</v>
       </c>
       <c r="G30">
-        <v>203.70815770015221</v>
+        <v>201.4601015957299</v>
       </c>
       <c r="H30">
-        <v>200.9118241362344</v>
+        <v>198.71284354233561</v>
       </c>
       <c r="I30">
-        <v>200.304936983495</v>
+        <v>198.45583808397791</v>
       </c>
       <c r="J30">
-        <v>203.5340383060713</v>
+        <v>201.39340969870199</v>
       </c>
       <c r="K30">
-        <v>217.28246505411909</v>
+        <v>214.68355235391769</v>
       </c>
       <c r="L30">
-        <v>220.05766352213899</v>
+        <v>217.1158806434336</v>
       </c>
       <c r="M30">
-        <v>233.44944446486539</v>
+        <v>231.78307640948981</v>
       </c>
       <c r="N30">
-        <v>243.7452101312897</v>
+        <v>241.29293087549689</v>
       </c>
       <c r="O30">
-        <v>257.38108396191308</v>
+        <v>255.8362139382518</v>
       </c>
       <c r="P30">
-        <v>275.27247923890388</v>
+        <v>274.31752805258452</v>
       </c>
       <c r="Q30">
-        <v>290.42530573870567</v>
+        <v>289.03612590356312</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2260,52 +2180,52 @@
         <v>46</v>
       </c>
       <c r="B31">
-        <v>218.39657149074489</v>
+        <v>218.33334417990309</v>
       </c>
       <c r="C31">
-        <v>233.73851913822139</v>
+        <v>234.59837037889099</v>
       </c>
       <c r="D31">
-        <v>225.33490274682589</v>
-      </c>
-      <c r="E31">
-        <v>211.93002126812809</v>
+        <v>225.7280097818325</v>
+      </c>
+      <c r="E31" s="2">
+        <v>212.12453277685901</v>
       </c>
       <c r="F31">
-        <v>202.84880955785579</v>
+        <v>202.74042503791031</v>
       </c>
       <c r="G31">
-        <v>202.41888586646581</v>
+        <v>202.30305868974099</v>
       </c>
       <c r="H31">
-        <v>199.95110778501649</v>
+        <v>199.17483494021471</v>
       </c>
       <c r="I31">
-        <v>200.03624405636961</v>
+        <v>199.20458917847029</v>
       </c>
       <c r="J31">
-        <v>202.89543197777459</v>
+        <v>201.8428748290907</v>
       </c>
       <c r="K31">
-        <v>215.37831907565501</v>
+        <v>213.3785229291565</v>
       </c>
       <c r="L31">
-        <v>224.19195879646699</v>
+        <v>221.3037302759233</v>
       </c>
       <c r="M31">
-        <v>236.64104677797721</v>
+        <v>232.61077767691509</v>
       </c>
       <c r="N31">
-        <v>249.6006202814431</v>
+        <v>244.96275854914421</v>
       </c>
       <c r="O31">
-        <v>254.03714956091471</v>
+        <v>249.2591014823214</v>
       </c>
       <c r="P31">
-        <v>252.99370257735899</v>
+        <v>248.83235794043941</v>
       </c>
       <c r="Q31">
-        <v>266.77600113364929</v>
+        <v>261.14319635534019</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2313,52 +2233,52 @@
         <v>47</v>
       </c>
       <c r="B32">
-        <v>209.9924285323782</v>
+        <v>208.9500964836262</v>
       </c>
       <c r="C32">
-        <v>238.30451130878521</v>
+        <v>238.70743723771119</v>
       </c>
       <c r="D32">
-        <v>220.10278247864341</v>
-      </c>
-      <c r="E32">
-        <v>208.05451596973251</v>
+        <v>220.65718236860141</v>
+      </c>
+      <c r="E32" s="2">
+        <v>207.75906130923471</v>
       </c>
       <c r="F32">
-        <v>197.18960035399081</v>
+        <v>196.9858071181863</v>
       </c>
       <c r="G32">
-        <v>192.41657461565319</v>
+        <v>192.65445488753679</v>
       </c>
       <c r="H32">
-        <v>189.6189969279084</v>
+        <v>189.673628982411</v>
       </c>
       <c r="I32">
-        <v>190.90517553792219</v>
+        <v>191.644156655995</v>
       </c>
       <c r="J32">
-        <v>199.87487715528971</v>
+        <v>200.79860417910501</v>
       </c>
       <c r="K32">
-        <v>199.92584349585059</v>
+        <v>199.85779540307979</v>
       </c>
       <c r="L32">
-        <v>200.05149147712979</v>
+        <v>199.94819218966381</v>
       </c>
       <c r="M32">
-        <v>208.00117393532881</v>
+        <v>208.0799854289406</v>
       </c>
       <c r="N32">
-        <v>223.11558386412671</v>
+        <v>222.6157502553088</v>
       </c>
       <c r="O32">
-        <v>228.40268223738391</v>
+        <v>229.02808463452459</v>
       </c>
       <c r="P32">
-        <v>232.66603853064171</v>
+        <v>233.2983943537283</v>
       </c>
       <c r="Q32">
-        <v>242.88717488743481</v>
+        <v>243.41095206154449</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2366,52 +2286,52 @@
         <v>48</v>
       </c>
       <c r="B33">
-        <v>209.98998428650799</v>
+        <v>208.38344098484029</v>
       </c>
       <c r="C33">
-        <v>239.29050490544591</v>
+        <v>238.41241580257829</v>
       </c>
       <c r="D33">
-        <v>221.30570726017001</v>
-      </c>
-      <c r="E33">
-        <v>208.60139511765351</v>
+        <v>220.56629909454389</v>
+      </c>
+      <c r="E33" s="2">
+        <v>207.45988234665421</v>
       </c>
       <c r="F33">
-        <v>197.52963604217709</v>
+        <v>196.2758587335363</v>
       </c>
       <c r="G33">
-        <v>192.35723702260651</v>
+        <v>192.09451515485631</v>
       </c>
       <c r="H33">
-        <v>189.7282484370719</v>
+        <v>189.4925604219714</v>
       </c>
       <c r="I33">
-        <v>191.43438169098121</v>
+        <v>190.70012721709679</v>
       </c>
       <c r="J33">
-        <v>201.10201427057871</v>
+        <v>199.1693287341343</v>
       </c>
       <c r="K33">
-        <v>200.8332415068852</v>
+        <v>198.37662954378629</v>
       </c>
       <c r="L33">
-        <v>201.3124843256158</v>
+        <v>198.04198335401821</v>
       </c>
       <c r="M33">
-        <v>208.77274614201579</v>
+        <v>205.81237323764671</v>
       </c>
       <c r="N33">
-        <v>223.58845064092051</v>
+        <v>219.32028522079921</v>
       </c>
       <c r="O33">
-        <v>231.28926122859571</v>
+        <v>226.04924870901951</v>
       </c>
       <c r="P33">
-        <v>236.10236376461879</v>
+        <v>230.4636160289653</v>
       </c>
       <c r="Q33">
-        <v>244.07773681036821</v>
+        <v>238.0711585374589</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -2419,52 +2339,52 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>208.54579931975201</v>
+        <v>207.82199943972921</v>
       </c>
       <c r="C34">
-        <v>238.0403554344995</v>
+        <v>238.09703936270279</v>
       </c>
       <c r="D34">
-        <v>219.83515251399189</v>
-      </c>
-      <c r="E34">
-        <v>206.9489689849942</v>
+        <v>220.27130277291661</v>
+      </c>
+      <c r="E34" s="2">
+        <v>207.74368575958511</v>
       </c>
       <c r="F34">
-        <v>196.2340688885518</v>
+        <v>196.2549158982211</v>
       </c>
       <c r="G34">
-        <v>191.58963399377851</v>
-      </c>
-      <c r="H34" s="2">
-        <v>188.55985528912461</v>
+        <v>191.50033690905019</v>
+      </c>
+      <c r="H34">
+        <v>188.82230047608579</v>
       </c>
       <c r="I34">
-        <v>189.70921770979709</v>
+        <v>190.40560130023121</v>
       </c>
       <c r="J34">
-        <v>199.14723389807671</v>
+        <v>198.82041653583889</v>
       </c>
       <c r="K34">
-        <v>199.27010676041991</v>
+        <v>198.04346390251419</v>
       </c>
       <c r="L34">
-        <v>198.493518223477</v>
+        <v>197.96111145523091</v>
       </c>
       <c r="M34">
-        <v>205.65250747419989</v>
+        <v>205.34907223220989</v>
       </c>
       <c r="N34">
-        <v>218.75861935588819</v>
+        <v>217.72428622952211</v>
       </c>
       <c r="O34">
-        <v>226.0477620008574</v>
+        <v>225.36392530081429</v>
       </c>
       <c r="P34">
-        <v>230.481733792651</v>
+        <v>229.66682702016351</v>
       </c>
       <c r="Q34">
-        <v>235.98559198135149</v>
+        <v>236.87098588893011</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -2472,52 +2392,52 @@
         <v>50</v>
       </c>
       <c r="B35">
-        <v>208.22118156888271</v>
+        <v>208.50239203854471</v>
       </c>
       <c r="C35">
-        <v>238.80511978451321</v>
+        <v>239.09592454901289</v>
       </c>
       <c r="D35">
-        <v>220.60467632822241</v>
-      </c>
-      <c r="E35">
-        <v>207.88705982104369</v>
-      </c>
-      <c r="F35">
-        <v>196.32721289848089</v>
+        <v>221.05254361355219</v>
+      </c>
+      <c r="E35" s="2">
+        <v>208.04939712730939</v>
+      </c>
+      <c r="F35" s="2">
+        <v>196.85153029572521</v>
       </c>
       <c r="G35">
-        <v>191.3618342617043</v>
+        <v>191.98365790995959</v>
       </c>
       <c r="H35">
-        <v>188.95013841062689</v>
+        <v>188.6104477807809</v>
       </c>
       <c r="I35">
-        <v>189.86795186738121</v>
+        <v>190.05177535282161</v>
       </c>
       <c r="J35">
-        <v>199.7602857981887</v>
+        <v>198.90395409549879</v>
       </c>
       <c r="K35">
-        <v>199.6775887574866</v>
+        <v>198.0329721726664</v>
       </c>
       <c r="L35">
-        <v>198.42605597360691</v>
+        <v>197.5352970992563</v>
       </c>
       <c r="M35">
-        <v>204.82368145091979</v>
+        <v>204.45749407759169</v>
       </c>
       <c r="N35">
-        <v>215.69136496073469</v>
+        <v>216.45847987944151</v>
       </c>
       <c r="O35">
-        <v>223.5815004669125</v>
+        <v>224.3091461518375</v>
       </c>
       <c r="P35">
-        <v>228.22987746067119</v>
+        <v>229.5974824918878</v>
       </c>
       <c r="Q35">
-        <v>229.92296183420049</v>
+        <v>231.35484057821569</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -2525,52 +2445,52 @@
         <v>51</v>
       </c>
       <c r="B36">
-        <v>208.7656828493792</v>
+        <v>207.78257078376649</v>
       </c>
       <c r="C36">
-        <v>238.78156515965571</v>
+        <v>238.28938170528971</v>
       </c>
       <c r="D36">
-        <v>220.53896482495981</v>
-      </c>
-      <c r="E36">
-        <v>207.51229527312961</v>
-      </c>
-      <c r="F36">
-        <v>196.59814210303449</v>
+        <v>219.99822545582231</v>
+      </c>
+      <c r="E36" s="2">
+        <v>207.19020846397351</v>
+      </c>
+      <c r="F36" s="2">
+        <v>195.87791857611799</v>
       </c>
       <c r="G36">
-        <v>192.11920756446489</v>
+        <v>191.09528486150879</v>
       </c>
       <c r="H36">
-        <v>189.31104113855619</v>
+        <v>188.4571822458341</v>
       </c>
       <c r="I36">
-        <v>191.09104835614019</v>
+        <v>189.3859903458353</v>
       </c>
       <c r="J36">
-        <v>200.4760610198328</v>
+        <v>197.8236130009478</v>
       </c>
       <c r="K36">
-        <v>199.88257912499401</v>
+        <v>198.15555283390469</v>
       </c>
       <c r="L36">
-        <v>199.54120528920029</v>
+        <v>198.28393167158541</v>
       </c>
       <c r="M36">
-        <v>210.89057782962379</v>
+        <v>209.4006298483736</v>
       </c>
       <c r="N36">
-        <v>223.7032835601938</v>
+        <v>222.07830871847699</v>
       </c>
       <c r="O36">
-        <v>228.58483583360871</v>
+        <v>226.01989977027091</v>
       </c>
       <c r="P36">
-        <v>232.24604134650019</v>
+        <v>229.7761267546301</v>
       </c>
       <c r="Q36">
-        <v>248.5104924113798</v>
+        <v>246.48229906716611</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -2578,52 +2498,52 @@
         <v>52</v>
       </c>
       <c r="B37">
-        <v>210.01576638455111</v>
+        <v>208.39987203462391</v>
       </c>
       <c r="C37">
-        <v>238.896304833404</v>
+        <v>239.01094773273559</v>
       </c>
       <c r="D37">
-        <v>220.80904693395649</v>
-      </c>
-      <c r="E37">
-        <v>207.69289133860499</v>
-      </c>
-      <c r="F37">
-        <v>196.76493848585</v>
+        <v>221.17038613090489</v>
+      </c>
+      <c r="E37" s="2">
+        <v>208.10859494094501</v>
+      </c>
+      <c r="F37" s="2">
+        <v>196.72109919521219</v>
       </c>
       <c r="G37">
-        <v>191.8816970125965</v>
+        <v>192.09399563536019</v>
       </c>
       <c r="H37">
-        <v>189.66108985232731</v>
+        <v>189.16162721124689</v>
       </c>
       <c r="I37">
-        <v>190.92828274884801</v>
+        <v>190.43895687695741</v>
       </c>
       <c r="J37">
-        <v>199.90255082043541</v>
+        <v>199.35399578428559</v>
       </c>
       <c r="K37">
-        <v>199.11793633019539</v>
+        <v>199.2527993036114</v>
       </c>
       <c r="L37">
-        <v>199.64965207182129</v>
+        <v>199.32198619136619</v>
       </c>
       <c r="M37">
-        <v>210.21877539527409</v>
+        <v>209.90740437367859</v>
       </c>
       <c r="N37">
-        <v>224.39729375053179</v>
+        <v>224.1550193649997</v>
       </c>
       <c r="O37">
-        <v>229.80241602187451</v>
+        <v>229.16815778474111</v>
       </c>
       <c r="P37">
-        <v>233.62466563926279</v>
+        <v>232.65121804295609</v>
       </c>
       <c r="Q37">
-        <v>247.65328679520991</v>
+        <v>247.46247540732381</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -2631,52 +2551,52 @@
         <v>53</v>
       </c>
       <c r="B38">
-        <v>209.82421631827259</v>
+        <v>210.21209331449251</v>
       </c>
       <c r="C38">
-        <v>238.53419192329599</v>
+        <v>238.65009250512011</v>
       </c>
       <c r="D38">
-        <v>220.6005494101278</v>
-      </c>
-      <c r="E38">
-        <v>208.02902556478699</v>
-      </c>
-      <c r="F38">
-        <v>196.81496344721961</v>
+        <v>220.82973807576309</v>
+      </c>
+      <c r="E38" s="2">
+        <v>208.6889274135427</v>
+      </c>
+      <c r="F38" s="2">
+        <v>197.21744457026489</v>
       </c>
       <c r="G38">
-        <v>192.09489703091609</v>
+        <v>192.21568902728211</v>
       </c>
       <c r="H38">
-        <v>189.27540820102371</v>
+        <v>189.84637529796009</v>
       </c>
       <c r="I38">
-        <v>190.87438134773649</v>
+        <v>192.02753237885011</v>
       </c>
       <c r="J38">
-        <v>200.4444384262338</v>
+        <v>200.84946511927231</v>
       </c>
       <c r="K38">
-        <v>199.39446578125219</v>
+        <v>199.82453695619711</v>
       </c>
       <c r="L38">
-        <v>199.48862323786389</v>
+        <v>200.1587054385042</v>
       </c>
       <c r="M38">
-        <v>209.90371258931839</v>
+        <v>209.42153758112451</v>
       </c>
       <c r="N38">
-        <v>225.10581436518461</v>
+        <v>224.36420772499969</v>
       </c>
       <c r="O38">
-        <v>230.87387953467959</v>
+        <v>230.137201849674</v>
       </c>
       <c r="P38">
-        <v>234.51059224096119</v>
+        <v>233.80328140956121</v>
       </c>
       <c r="Q38">
-        <v>245.80395362855921</v>
+        <v>245.8846086977737</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -2684,52 +2604,52 @@
         <v>54</v>
       </c>
       <c r="B39">
-        <v>208.0816103082123</v>
+        <v>208.65789842323699</v>
       </c>
       <c r="C39">
-        <v>238.98571816511651</v>
+        <v>239.07172552441409</v>
       </c>
       <c r="D39">
-        <v>220.99011569613441</v>
-      </c>
-      <c r="E39">
-        <v>208.20728521955019</v>
-      </c>
-      <c r="F39">
-        <v>196.9166541438365</v>
+        <v>221.09677666905549</v>
+      </c>
+      <c r="E39" s="2">
+        <v>208.50316613663489</v>
+      </c>
+      <c r="F39" s="2">
+        <v>197.13513274788039</v>
       </c>
       <c r="G39">
-        <v>192.2730417615235</v>
+        <v>192.18941537181209</v>
       </c>
       <c r="H39">
-        <v>189.50989511930891</v>
+        <v>189.54911455927811</v>
       </c>
       <c r="I39">
-        <v>190.70332602745489</v>
+        <v>190.88163672876581</v>
       </c>
       <c r="J39">
-        <v>200.09502736871571</v>
+        <v>199.22911138680749</v>
       </c>
       <c r="K39">
-        <v>199.39093717619679</v>
+        <v>198.70444212652799</v>
       </c>
       <c r="L39">
-        <v>200.50795205823701</v>
+        <v>198.57892306474599</v>
       </c>
       <c r="M39">
-        <v>209.60370597679929</v>
+        <v>208.91863875882581</v>
       </c>
       <c r="N39">
-        <v>224.9985197729026</v>
+        <v>223.68895077475599</v>
       </c>
       <c r="O39">
-        <v>231.2475249772327</v>
+        <v>230.49314627203469</v>
       </c>
       <c r="P39">
-        <v>233.76840151801281</v>
+        <v>234.00636917758379</v>
       </c>
       <c r="Q39">
-        <v>243.0607186386828</v>
+        <v>246.26050754648139</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -2737,52 +2657,52 @@
         <v>55</v>
       </c>
       <c r="B40">
-        <v>209.1346670472503</v>
+        <v>208.37160112380741</v>
       </c>
       <c r="C40">
-        <v>239.5169692392854</v>
+        <v>238.5878685314411</v>
       </c>
       <c r="D40">
-        <v>221.23225404611429</v>
-      </c>
-      <c r="E40">
-        <v>208.54812249722281</v>
-      </c>
-      <c r="F40">
-        <v>197.23629625000979</v>
+        <v>220.32058030526949</v>
+      </c>
+      <c r="E40" s="2">
+        <v>207.5794692712407</v>
+      </c>
+      <c r="F40" s="2">
+        <v>196.50965853504539</v>
       </c>
       <c r="G40">
-        <v>191.81168338645739</v>
+        <v>192.27492623889981</v>
       </c>
       <c r="H40">
-        <v>189.4250840149945</v>
+        <v>188.59269790171749</v>
       </c>
       <c r="I40">
-        <v>190.23999864449351</v>
+        <v>190.2636633219891</v>
       </c>
       <c r="J40">
-        <v>199.66319974069381</v>
+        <v>199.06255037998241</v>
       </c>
       <c r="K40">
-        <v>199.02472414793121</v>
+        <v>198.8472745027201</v>
       </c>
       <c r="L40">
-        <v>198.4189778452737</v>
+        <v>197.9369547198051</v>
       </c>
       <c r="M40">
-        <v>205.6021751460955</v>
+        <v>204.63424532911671</v>
       </c>
       <c r="N40">
-        <v>217.1670880190963</v>
+        <v>216.45760596915849</v>
       </c>
       <c r="O40">
-        <v>224.848278320986</v>
+        <v>224.45272026043639</v>
       </c>
       <c r="P40">
-        <v>229.51745316780131</v>
+        <v>228.84350155986431</v>
       </c>
       <c r="Q40">
-        <v>233.62137794625221</v>
+        <v>232.67154850555829</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -2790,52 +2710,52 @@
         <v>56</v>
       </c>
       <c r="B41">
-        <v>218.61526165458369</v>
+        <v>219.9895214989441</v>
       </c>
       <c r="C41">
-        <v>235.8858258673383</v>
+        <v>235.6357007508455</v>
       </c>
       <c r="D41">
-        <v>223.67812267526281</v>
-      </c>
-      <c r="E41">
-        <v>204.8805701994134</v>
-      </c>
-      <c r="F41">
-        <v>201.4215506145695</v>
+        <v>224.82694698660691</v>
+      </c>
+      <c r="E41" s="2">
+        <v>205.17205877141851</v>
+      </c>
+      <c r="F41" s="2">
+        <v>201.64924137293141</v>
       </c>
       <c r="G41">
-        <v>214.27714677929961</v>
+        <v>214.29681833144531</v>
       </c>
       <c r="H41">
-        <v>217.54802375162919</v>
+        <v>217.41211481651359</v>
       </c>
       <c r="I41">
-        <v>213.48342631849269</v>
+        <v>212.7101162499329</v>
       </c>
       <c r="J41">
-        <v>219.61618305567151</v>
+        <v>218.5486769379562</v>
       </c>
       <c r="K41">
-        <v>234.4035967431598</v>
+        <v>233.38584878670409</v>
       </c>
       <c r="L41">
-        <v>246.1989659634398</v>
+        <v>245.7967937155953</v>
       </c>
       <c r="M41">
-        <v>256.39845318735991</v>
+        <v>255.2944981426692</v>
       </c>
       <c r="N41">
-        <v>265.65316402916051</v>
+        <v>264.03922681012409</v>
       </c>
       <c r="O41">
-        <v>271.56206636731412</v>
+        <v>269.64322294438671</v>
       </c>
       <c r="P41">
-        <v>279.11409655910808</v>
+        <v>277.16443158788542</v>
       </c>
       <c r="Q41">
-        <v>284.57754113845601</v>
+        <v>281.78771960321632</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -2843,52 +2763,52 @@
         <v>57</v>
       </c>
       <c r="B42">
-        <v>217.001951839085</v>
+        <v>218.55411666699371</v>
       </c>
       <c r="C42">
-        <v>235.1324765935546</v>
-      </c>
-      <c r="D42">
-        <v>219.95498194682389</v>
-      </c>
-      <c r="E42">
-        <v>201.76362654513849</v>
+        <v>235.44532479397279</v>
+      </c>
+      <c r="D42" s="2">
+        <v>221.21358584736561</v>
+      </c>
+      <c r="E42" s="2">
+        <v>202.69368669688029</v>
       </c>
       <c r="F42">
-        <v>200.34556755181339</v>
+        <v>201.4275468873679</v>
       </c>
       <c r="G42">
-        <v>208.25463889413649</v>
+        <v>210.31296520667161</v>
       </c>
       <c r="H42">
-        <v>215.1815867980946</v>
+        <v>216.65311084547409</v>
       </c>
       <c r="I42">
-        <v>204.2518881421552</v>
+        <v>205.0742950418402</v>
       </c>
       <c r="J42">
-        <v>211.7794992945106</v>
+        <v>211.81427940385521</v>
       </c>
       <c r="K42">
-        <v>223.4546430435374</v>
+        <v>222.48904610392009</v>
       </c>
       <c r="L42">
-        <v>230.51207594949889</v>
+        <v>229.47145425269619</v>
       </c>
       <c r="M42">
-        <v>234.97318137811709</v>
+        <v>234.17043223333869</v>
       </c>
       <c r="N42">
-        <v>245.83676072053129</v>
+        <v>244.8646663532171</v>
       </c>
       <c r="O42">
-        <v>256.38541995734238</v>
+        <v>256.11246591502629</v>
       </c>
       <c r="P42">
-        <v>269.60428693118519</v>
+        <v>268.49540993708843</v>
       </c>
       <c r="Q42">
-        <v>280.95920876306621</v>
+        <v>280.79130345023282</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2896,52 +2816,52 @@
         <v>58</v>
       </c>
       <c r="B43">
-        <v>217.38958176150129</v>
+        <v>218.00568111810881</v>
       </c>
       <c r="C43">
-        <v>234.8601421334038</v>
+        <v>234.95261002273691</v>
       </c>
       <c r="D43">
-        <v>220.06149385833541</v>
-      </c>
-      <c r="E43">
-        <v>201.35752741236021</v>
-      </c>
-      <c r="F43">
-        <v>200.073017236639</v>
+        <v>220.29419875061171</v>
+      </c>
+      <c r="E43" s="2">
+        <v>202.83972055576021</v>
+      </c>
+      <c r="F43" s="2">
+        <v>201.2623650979364</v>
       </c>
       <c r="G43">
-        <v>205.53591180038319</v>
+        <v>206.35282907963989</v>
       </c>
       <c r="H43">
-        <v>210.88704004677879</v>
+        <v>213.19073682424269</v>
       </c>
       <c r="I43">
-        <v>204.7337138859894</v>
+        <v>207.015309746127</v>
       </c>
       <c r="J43">
-        <v>212.60495390301051</v>
+        <v>214.97829251340059</v>
       </c>
       <c r="K43">
-        <v>223.80760453197109</v>
+        <v>226.21331746171461</v>
       </c>
       <c r="L43">
-        <v>235.67478369920499</v>
+        <v>237.87774856935971</v>
       </c>
       <c r="M43">
-        <v>244.32387803901011</v>
+        <v>246.06392741254231</v>
       </c>
       <c r="N43">
-        <v>257.81047288800801</v>
+        <v>260.67043242913837</v>
       </c>
       <c r="O43">
-        <v>263.88900035637408</v>
+        <v>266.31384335550479</v>
       </c>
       <c r="P43">
-        <v>267.10267649826193</v>
+        <v>268.71159502660993</v>
       </c>
       <c r="Q43">
-        <v>274.48404434661052</v>
+        <v>277.37514683444653</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -2949,52 +2869,52 @@
         <v>59</v>
       </c>
       <c r="B44">
-        <v>244.90553422367771</v>
+        <v>245.56603292326619</v>
       </c>
       <c r="C44">
-        <v>246.81652950292329</v>
+        <v>246.3289588357465</v>
       </c>
       <c r="D44">
-        <v>245.26273147587901</v>
+        <v>245.7619751654411</v>
       </c>
       <c r="E44">
-        <v>236.7601825327599</v>
+        <v>238.11855747084121</v>
       </c>
       <c r="F44">
-        <v>228.7125421355077</v>
+        <v>228.64756491601949</v>
       </c>
       <c r="G44">
-        <v>218.96767147344809</v>
+        <v>217.46876633668771</v>
       </c>
       <c r="H44">
-        <v>219.7484370542098</v>
+        <v>217.76240384978789</v>
       </c>
       <c r="I44">
-        <v>231.4335683542393</v>
+        <v>229.27831020948369</v>
       </c>
       <c r="J44">
-        <v>236.33482748203741</v>
+        <v>234.3204090132578</v>
       </c>
       <c r="K44">
-        <v>243.60107821449139</v>
+        <v>241.7640470789128</v>
       </c>
       <c r="L44">
-        <v>255.46438354214911</v>
+        <v>254.12860171565029</v>
       </c>
       <c r="M44">
-        <v>273.03350779855089</v>
+        <v>271.06368926847739</v>
       </c>
       <c r="N44">
-        <v>290.94947322567202</v>
+        <v>289.41141492945133</v>
       </c>
       <c r="O44">
-        <v>302.28173819036641</v>
+        <v>301.68646861789568</v>
       </c>
       <c r="P44">
-        <v>315.43354873078431</v>
+        <v>315.9946644536771</v>
       </c>
       <c r="Q44">
-        <v>328.12887502593981</v>
+        <v>329.49210165800122</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -3002,52 +2922,52 @@
         <v>60</v>
       </c>
       <c r="B45">
-        <v>252.25642367777621</v>
+        <v>251.97452497124351</v>
       </c>
       <c r="C45">
-        <v>252.27402023365281</v>
+        <v>251.93764025136539</v>
       </c>
       <c r="D45">
-        <v>245.16420227488359</v>
+        <v>244.77463405696491</v>
       </c>
       <c r="E45">
-        <v>256.70047795528012</v>
+        <v>256.26073073453807</v>
       </c>
       <c r="F45">
-        <v>270.82500735943449</v>
+        <v>269.75932563721022</v>
       </c>
       <c r="G45">
-        <v>285.04319774901342</v>
+        <v>282.74181947192568</v>
       </c>
       <c r="H45">
-        <v>283.85204471054988</v>
+        <v>281.94943188530061</v>
       </c>
       <c r="I45">
-        <v>276.53606514110788</v>
+        <v>274.71653786101132</v>
       </c>
       <c r="J45">
-        <v>273.13799930867663</v>
+        <v>272.52011535218048</v>
       </c>
       <c r="K45">
-        <v>273.32355092991821</v>
+        <v>272.29209330157369</v>
       </c>
       <c r="L45">
-        <v>286.69358809820437</v>
+        <v>285.24714383414721</v>
       </c>
       <c r="M45">
-        <v>305.47212013959592</v>
+        <v>303.95141688360582</v>
       </c>
       <c r="N45">
-        <v>314.7114305035285</v>
+        <v>314.14073486838328</v>
       </c>
       <c r="O45">
-        <v>321.12127922818382</v>
+        <v>320.74660950861937</v>
       </c>
       <c r="P45">
-        <v>329.93818311720861</v>
+        <v>329.53494027191539</v>
       </c>
       <c r="Q45">
-        <v>331.56389296189832</v>
+        <v>330.02266530441051</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3055,52 +2975,52 @@
         <v>61</v>
       </c>
       <c r="B46">
-        <v>257.18830568913478</v>
+        <v>258.20625503178331</v>
       </c>
       <c r="C46">
-        <v>262.92175321557522</v>
+        <v>262.28603024192103</v>
       </c>
       <c r="D46">
-        <v>246.13212467596571</v>
+        <v>246.03448513787899</v>
       </c>
       <c r="E46">
-        <v>251.38761896598021</v>
+        <v>251.7588677354172</v>
       </c>
       <c r="F46">
-        <v>249.12432230644851</v>
+        <v>249.8458341910958</v>
       </c>
       <c r="G46">
-        <v>251.14768851825951</v>
+        <v>250.36384914187289</v>
       </c>
       <c r="H46">
-        <v>246.55494523084769</v>
+        <v>246.38638253431139</v>
       </c>
       <c r="I46">
-        <v>242.335750704883</v>
+        <v>241.35737357128411</v>
       </c>
       <c r="J46">
-        <v>253.88033113719951</v>
+        <v>252.44182921353749</v>
       </c>
       <c r="K46">
-        <v>264.48683944434532</v>
+        <v>262.24998358463853</v>
       </c>
       <c r="L46">
-        <v>278.75257336388091</v>
+        <v>276.45149015606762</v>
       </c>
       <c r="M46">
-        <v>283.38874041145311</v>
+        <v>280.97508974810933</v>
       </c>
       <c r="N46">
-        <v>286.20990380189079</v>
+        <v>282.67424209884268</v>
       </c>
       <c r="O46">
-        <v>291.29840044069857</v>
+        <v>287.29696670698519</v>
       </c>
       <c r="P46">
-        <v>296.30102417218552</v>
+        <v>292.73376495034557</v>
       </c>
       <c r="Q46">
-        <v>302.77658716392051</v>
+        <v>297.92269383290989</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3108,57 +3028,57 @@
         <v>62</v>
       </c>
       <c r="B47">
-        <v>247.3375550398051</v>
+        <v>247.64235309670559</v>
       </c>
       <c r="C47">
-        <v>245.13983841478321</v>
+        <v>245.03440038502151</v>
       </c>
       <c r="D47">
-        <v>251.6167376598668</v>
+        <v>251.49773845173189</v>
       </c>
       <c r="E47">
-        <v>255.36636369077351</v>
+        <v>255.15880463461161</v>
       </c>
       <c r="F47">
-        <v>262.74212114899922</v>
+        <v>263.12443789334128</v>
       </c>
       <c r="G47">
-        <v>274.28250319282301</v>
+        <v>275.81551800874257</v>
       </c>
       <c r="H47">
-        <v>272.42270312909619</v>
+        <v>273.14806534918262</v>
       </c>
       <c r="I47">
-        <v>251.62211231079519</v>
+        <v>252.36382881190701</v>
       </c>
       <c r="J47">
-        <v>246.07728609772619</v>
+        <v>247.47395174403499</v>
       </c>
       <c r="K47">
-        <v>251.6321654850955</v>
+        <v>254.18140180493401</v>
       </c>
       <c r="L47">
-        <v>266.24972586729479</v>
+        <v>269.56955782750049</v>
       </c>
       <c r="M47">
-        <v>272.38491671124302</v>
+        <v>274.33839755725847</v>
       </c>
       <c r="N47">
-        <v>276.02128249162843</v>
+        <v>278.00656984491832</v>
       </c>
       <c r="O47">
-        <v>278.47267127379519</v>
+        <v>279.26928837223528</v>
       </c>
       <c r="P47">
-        <v>277.78321984256672</v>
+        <v>278.13441129280147</v>
       </c>
       <c r="Q47">
-        <v>278.31625248751533</v>
+        <v>278.42171613103221</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q33 C35:Q47 C34:G34 I34:Q34">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="C2:Q47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3168,10 +3088,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="2" priority="1" bottom="1" rank="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19:Q33 C35:Q47 C34:G34 I34:Q34">
-    <cfRule type="top10" dxfId="4" priority="2" bottom="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_RMSEP.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\trans.beta.carotenes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -247,51 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -333,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -365,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -400,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,2519 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>254.8396153847788</v>
+        <v>255.8505260375109</v>
       </c>
       <c r="C2">
-        <v>288.00277910478218</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D2">
-        <v>254.32743711924559</v>
+        <v>288.1602509846354</v>
       </c>
       <c r="E2">
-        <v>248.51223729117709</v>
+        <v>254.2808290319797</v>
       </c>
       <c r="F2">
-        <v>241.9878516363826</v>
+        <v>247.8180545517287</v>
       </c>
       <c r="G2">
-        <v>245.24922387558311</v>
+        <v>241.3967938790555</v>
       </c>
       <c r="H2">
-        <v>241.26860014619149</v>
+        <v>244.3686099127606</v>
       </c>
       <c r="I2">
-        <v>242.7509855430788</v>
+        <v>240.8882012231755</v>
       </c>
       <c r="J2">
-        <v>243.2334362639441</v>
+        <v>242.6539399600644</v>
       </c>
       <c r="K2">
-        <v>242.46669473278899</v>
+        <v>242.2902913012512</v>
       </c>
       <c r="L2">
-        <v>243.3122327118233</v>
+        <v>241.2905773581415</v>
       </c>
       <c r="M2">
-        <v>252.3774831911758</v>
+        <v>242.7472431968129</v>
       </c>
       <c r="N2">
-        <v>261.6451748996675</v>
+        <v>253.1770230708956</v>
       </c>
       <c r="O2">
-        <v>269.11559455272823</v>
+        <v>263.2962026037491</v>
       </c>
       <c r="P2">
-        <v>280.18125155433182</v>
+        <v>272.3415568157296</v>
       </c>
       <c r="Q2">
-        <v>272.49857921212117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>284.8769418336337</v>
+      </c>
+      <c r="R2">
+        <v>277.0961658743885</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>262.86936728461518</v>
+        <v>263.2641797548599</v>
       </c>
       <c r="C3">
-        <v>265.3360868800047</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D3">
-        <v>250.65026776909309</v>
+        <v>265.5150554716384</v>
       </c>
       <c r="E3">
-        <v>251.61323607944809</v>
+        <v>251.1646333503027</v>
       </c>
       <c r="F3">
-        <v>249.10607641981181</v>
+        <v>252.3894830678343</v>
       </c>
       <c r="G3">
-        <v>248.85070697864381</v>
+        <v>250.571671607058</v>
       </c>
       <c r="H3">
-        <v>246.33993620924161</v>
+        <v>252.1718655872997</v>
       </c>
       <c r="I3">
-        <v>254.5839346137077</v>
+        <v>250.0100933746004</v>
       </c>
       <c r="J3">
-        <v>257.53333805852913</v>
+        <v>259.3935745003104</v>
       </c>
       <c r="K3">
-        <v>261.62328993807381</v>
+        <v>261.4656036059325</v>
       </c>
       <c r="L3">
-        <v>265.97615270918692</v>
+        <v>265.5766517603609</v>
       </c>
       <c r="M3">
-        <v>274.30856261085052</v>
+        <v>268.5761016511441</v>
       </c>
       <c r="N3">
-        <v>291.62424381677607</v>
+        <v>277.2820812759899</v>
       </c>
       <c r="O3">
-        <v>309.38617201777288</v>
+        <v>295.885001943969</v>
       </c>
       <c r="P3">
-        <v>319.8943999093255</v>
+        <v>312.5477608253063</v>
       </c>
       <c r="Q3">
-        <v>331.73663245933568</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>322.5067092265649</v>
+      </c>
+      <c r="R3">
+        <v>332.5665183885381</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>261.93271175084487</v>
+        <v>263.4717294011078</v>
       </c>
       <c r="C4">
-        <v>283.28719939984012</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D4">
-        <v>255.9395740231927</v>
+        <v>284.2560736798804</v>
       </c>
       <c r="E4">
-        <v>252.81585606728231</v>
+        <v>257.0177524351153</v>
       </c>
       <c r="F4">
-        <v>253.7015967785386</v>
+        <v>254.1429102320567</v>
       </c>
       <c r="G4">
-        <v>246.25120494574929</v>
+        <v>255.3673333864176</v>
       </c>
       <c r="H4">
-        <v>235.3880574291058</v>
+        <v>247.4843982507118</v>
       </c>
       <c r="I4">
-        <v>231.53078615796619</v>
+        <v>237.4090173862412</v>
       </c>
       <c r="J4">
-        <v>240.67665942042839</v>
+        <v>233.0283957146456</v>
       </c>
       <c r="K4">
-        <v>252.02724649887969</v>
+        <v>242.329582659667</v>
       </c>
       <c r="L4">
-        <v>259.85009285220099</v>
+        <v>253.3847666260407</v>
       </c>
       <c r="M4">
-        <v>278.31983238335141</v>
+        <v>260.3762342756325</v>
       </c>
       <c r="N4">
-        <v>276.40736357787449</v>
+        <v>280.07229745977</v>
       </c>
       <c r="O4">
-        <v>267.41217060483871</v>
+        <v>278.3159519728756</v>
       </c>
       <c r="P4">
-        <v>261.30566269378988</v>
+        <v>269.263777827638</v>
       </c>
       <c r="Q4">
-        <v>260.59476673451002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>263.3621026333234</v>
+      </c>
+      <c r="R4">
+        <v>261.9925885885999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>255.00603467320889</v>
+        <v>255.7252287349815</v>
       </c>
       <c r="C5">
-        <v>252.86806461560789</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D5">
-        <v>251.6194540677059</v>
+        <v>253.0276401612984</v>
       </c>
       <c r="E5">
-        <v>249.98590042330471</v>
+        <v>251.9890788441642</v>
       </c>
       <c r="F5">
-        <v>244.00863616537299</v>
+        <v>250.4018028250325</v>
       </c>
       <c r="G5">
-        <v>245.42288303244851</v>
+        <v>245.7148145894498</v>
       </c>
       <c r="H5">
-        <v>243.90269937583889</v>
+        <v>247.6582655501801</v>
       </c>
       <c r="I5">
-        <v>244.421794877948</v>
+        <v>245.6944544758756</v>
       </c>
       <c r="J5">
-        <v>252.42103837222791</v>
+        <v>245.3799744825926</v>
       </c>
       <c r="K5">
-        <v>260.51052656332479</v>
+        <v>253.9855499601439</v>
       </c>
       <c r="L5">
-        <v>269.76563020707329</v>
+        <v>261.3678052237454</v>
       </c>
       <c r="M5">
-        <v>277.86897251746927</v>
+        <v>271.8066770201959</v>
       </c>
       <c r="N5">
-        <v>281.21553790226938</v>
+        <v>280.2341517496714</v>
       </c>
       <c r="O5">
-        <v>274.6898758316392</v>
+        <v>281.8935149087517</v>
       </c>
       <c r="P5">
-        <v>273.24416398639607</v>
+        <v>275.110405520462</v>
       </c>
       <c r="Q5">
-        <v>268.19087405167102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>271.7546687564699</v>
+      </c>
+      <c r="R5">
+        <v>267.5633740202848</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>254.2078443442515</v>
+        <v>256.1844314767317</v>
       </c>
       <c r="C6">
-        <v>252.00496448660471</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D6">
-        <v>250.96139647172279</v>
+        <v>252.5754322974177</v>
       </c>
       <c r="E6">
-        <v>249.4981779651302</v>
+        <v>252.0215130765159</v>
       </c>
       <c r="F6">
-        <v>247.01531787666329</v>
+        <v>250.4230968293872</v>
       </c>
       <c r="G6">
-        <v>239.53439443604779</v>
+        <v>247.0961795921543</v>
       </c>
       <c r="H6">
-        <v>243.49367463246719</v>
+        <v>238.4895994864031</v>
       </c>
       <c r="I6">
-        <v>245.5859925215924</v>
+        <v>242.7679019702272</v>
       </c>
       <c r="J6">
-        <v>257.36078261234758</v>
+        <v>244.6330038950946</v>
       </c>
       <c r="K6">
-        <v>268.1299966926544</v>
+        <v>256.5347371335315</v>
       </c>
       <c r="L6">
-        <v>274.12140200387228</v>
+        <v>267.4959441979575</v>
       </c>
       <c r="M6">
-        <v>281.6606602593713</v>
+        <v>272.3424831992677</v>
       </c>
       <c r="N6">
-        <v>281.89704864284198</v>
+        <v>280.91463906498</v>
       </c>
       <c r="O6">
-        <v>285.46257912736661</v>
+        <v>280.7845548581079</v>
       </c>
       <c r="P6">
-        <v>280.89672482648109</v>
+        <v>284.3375496127671</v>
       </c>
       <c r="Q6">
-        <v>278.62867147060172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>278.3848274887174</v>
+      </c>
+      <c r="R6">
+        <v>277.1205043763435</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>250.64327235865181</v>
+        <v>249.8641495853236</v>
       </c>
       <c r="C7">
-        <v>284.33566257872729</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D7">
-        <v>253.66270157609949</v>
+        <v>284.667989708012</v>
       </c>
       <c r="E7">
-        <v>239.012250957405</v>
+        <v>253.8503779011571</v>
       </c>
       <c r="F7">
-        <v>229.5859160039407</v>
+        <v>239.2427676057844</v>
       </c>
       <c r="G7">
-        <v>227.90116021891791</v>
+        <v>229.5354622858009</v>
       </c>
       <c r="H7">
-        <v>228.17763663949859</v>
+        <v>228.5587090104108</v>
       </c>
       <c r="I7">
-        <v>230.69419597900961</v>
+        <v>229.2653901535771</v>
       </c>
       <c r="J7">
-        <v>229.6777342029427</v>
+        <v>232.4796440760642</v>
       </c>
       <c r="K7">
-        <v>238.62182361691649</v>
+        <v>231.7234789400662</v>
       </c>
       <c r="L7">
-        <v>249.29777274754389</v>
+        <v>240.5656763789187</v>
       </c>
       <c r="M7">
-        <v>255.62357634791351</v>
+        <v>253.0878834598172</v>
       </c>
       <c r="N7">
-        <v>264.90372293128689</v>
+        <v>259.6516148445994</v>
       </c>
       <c r="O7">
-        <v>265.01918732025212</v>
+        <v>268.7271901390078</v>
       </c>
       <c r="P7">
-        <v>259.44020924548261</v>
+        <v>268.489127857532</v>
       </c>
       <c r="Q7">
-        <v>255.07273666426829</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>262.268325463919</v>
+      </c>
+      <c r="R7">
+        <v>258.5468754786897</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>264.25236841052492</v>
+        <v>263.6028442955144</v>
       </c>
       <c r="C8">
-        <v>273.75021062871878</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D8">
-        <v>258.34065409053977</v>
+        <v>272.6710211394377</v>
       </c>
       <c r="E8">
-        <v>245.1257254505588</v>
+        <v>257.5691286723359</v>
       </c>
       <c r="F8">
-        <v>243.08201975539581</v>
+        <v>244.4512869513748</v>
       </c>
       <c r="G8">
-        <v>242.14221240243549</v>
+        <v>242.5382481099993</v>
       </c>
       <c r="H8">
-        <v>242.23847297651639</v>
+        <v>241.8157884489808</v>
       </c>
       <c r="I8">
-        <v>239.0367102842379</v>
+        <v>242.7750136756794</v>
       </c>
       <c r="J8">
-        <v>243.77015980174409</v>
+        <v>240.3363043710683</v>
       </c>
       <c r="K8">
-        <v>252.01002005873261</v>
+        <v>244.7243688351747</v>
       </c>
       <c r="L8">
-        <v>266.07326855811522</v>
+        <v>253.3108006946577</v>
       </c>
       <c r="M8">
-        <v>277.62183320380592</v>
+        <v>267.3833718044342</v>
       </c>
       <c r="N8">
-        <v>277.45421976589381</v>
+        <v>278.885084109837</v>
       </c>
       <c r="O8">
-        <v>270.12846724301659</v>
+        <v>277.9864595189666</v>
       </c>
       <c r="P8">
-        <v>263.77566950792391</v>
+        <v>269.2695635194261</v>
       </c>
       <c r="Q8">
-        <v>268.02803899113923</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>262.7943941092142</v>
+      </c>
+      <c r="R8">
+        <v>266.8791014481221</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>261.33549674174492</v>
+        <v>265.9848181410143</v>
       </c>
       <c r="C9">
-        <v>272.71912740974091</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D9">
-        <v>257.20852384939258</v>
+        <v>273.9429481910408</v>
       </c>
       <c r="E9">
-        <v>243.97296513394471</v>
+        <v>258.9351849622777</v>
       </c>
       <c r="F9">
-        <v>242.39493764228069</v>
+        <v>245.7282277081821</v>
       </c>
       <c r="G9">
-        <v>241.90119322547599</v>
+        <v>243.9676693600766</v>
       </c>
       <c r="H9">
-        <v>243.18072690003669</v>
+        <v>243.2370887333997</v>
       </c>
       <c r="I9">
-        <v>239.62664046456121</v>
+        <v>244.1682973145864</v>
       </c>
       <c r="J9">
-        <v>243.67053427252</v>
+        <v>240.8262246892981</v>
       </c>
       <c r="K9">
-        <v>247.50624762108581</v>
+        <v>243.9495778510518</v>
       </c>
       <c r="L9">
-        <v>255.71085499719041</v>
+        <v>248.8228097733572</v>
       </c>
       <c r="M9">
-        <v>266.95452412206322</v>
+        <v>257.0717693619277</v>
       </c>
       <c r="N9">
-        <v>267.13062839694089</v>
+        <v>269.3782185940738</v>
       </c>
       <c r="O9">
-        <v>258.81487205114001</v>
+        <v>269.5353661972197</v>
       </c>
       <c r="P9">
-        <v>251.2418640273502</v>
+        <v>260.9894608299468</v>
       </c>
       <c r="Q9">
-        <v>256.08341761141583</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>253.3599365642592</v>
+      </c>
+      <c r="R9">
+        <v>259.7305492924756</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>264.50253039006247</v>
+        <v>262.7615713497141</v>
       </c>
       <c r="C10">
-        <v>273.94423099576642</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D10">
-        <v>259.60090304937881</v>
+        <v>273.023933929871</v>
       </c>
       <c r="E10">
-        <v>246.18346836760369</v>
+        <v>257.731496508719</v>
       </c>
       <c r="F10">
-        <v>245.1632665298215</v>
+        <v>243.7577642008189</v>
       </c>
       <c r="G10">
-        <v>244.67073541975449</v>
+        <v>242.3419582678093</v>
       </c>
       <c r="H10">
-        <v>245.49597779900219</v>
+        <v>241.72585287066</v>
       </c>
       <c r="I10">
-        <v>241.61866822395851</v>
+        <v>242.5078472721376</v>
       </c>
       <c r="J10">
-        <v>244.91225098649321</v>
+        <v>239.1908708891426</v>
       </c>
       <c r="K10">
-        <v>249.23641444805011</v>
+        <v>241.8504137707233</v>
       </c>
       <c r="L10">
-        <v>256.11498430127102</v>
+        <v>246.5134075971484</v>
       </c>
       <c r="M10">
-        <v>267.37864363792318</v>
+        <v>254.2473276217762</v>
       </c>
       <c r="N10">
-        <v>267.78388237686443</v>
+        <v>267.2086609135071</v>
       </c>
       <c r="O10">
-        <v>260.46898185872237</v>
+        <v>267.2224874015287</v>
       </c>
       <c r="P10">
-        <v>252.1727773113916</v>
+        <v>258.6603039775534</v>
       </c>
       <c r="Q10">
-        <v>256.92132353703113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>250.5395760342103</v>
+      </c>
+      <c r="R10">
+        <v>256.2398511848978</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>262.81850500538081</v>
+        <v>264.1768434688894</v>
       </c>
       <c r="C11">
-        <v>272.29577688535818</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D11">
-        <v>256.75520431968778</v>
+        <v>272.8703562045999</v>
       </c>
       <c r="E11">
-        <v>243.51206882948199</v>
+        <v>257.6497774360317</v>
       </c>
       <c r="F11">
-        <v>241.56647897275991</v>
+        <v>245.4158686489093</v>
       </c>
       <c r="G11">
-        <v>241.0353216829505</v>
+        <v>243.3925666487463</v>
       </c>
       <c r="H11">
-        <v>241.70289745348381</v>
+        <v>242.7218013180373</v>
       </c>
       <c r="I11">
-        <v>238.3811127313233</v>
+        <v>243.8346568775926</v>
       </c>
       <c r="J11">
-        <v>241.53599241799569</v>
+        <v>240.1022293266833</v>
       </c>
       <c r="K11">
-        <v>246.02840353944029</v>
+        <v>243.4360761113565</v>
       </c>
       <c r="L11">
-        <v>255.14592855979879</v>
+        <v>247.8271199014223</v>
       </c>
       <c r="M11">
-        <v>268.90639059933</v>
+        <v>256.8290688695384</v>
       </c>
       <c r="N11">
-        <v>269.84889047924872</v>
+        <v>270.0794440355086</v>
       </c>
       <c r="O11">
-        <v>260.95372763845421</v>
+        <v>270.8917740603653</v>
       </c>
       <c r="P11">
-        <v>252.4088813810184</v>
+        <v>261.7128635117551</v>
       </c>
       <c r="Q11">
-        <v>254.83943148453929</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>253.214615383198</v>
+      </c>
+      <c r="R11">
+        <v>255.8242312611721</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>252.62724044445869</v>
+        <v>251.4088257915272</v>
       </c>
       <c r="C12">
-        <v>251.19622354899499</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D12">
-        <v>248.6246429529636</v>
+        <v>249.7884077115265</v>
       </c>
       <c r="E12">
-        <v>241.77054614406521</v>
+        <v>246.840548510428</v>
       </c>
       <c r="F12">
-        <v>235.41559389663971</v>
+        <v>239.6104100078723</v>
       </c>
       <c r="G12">
-        <v>234.48194607158351</v>
+        <v>234.0590078139298</v>
       </c>
       <c r="H12">
-        <v>234.66642706208731</v>
+        <v>233.4591177747463</v>
       </c>
       <c r="I12">
-        <v>235.95441612348421</v>
+        <v>233.312794073574</v>
       </c>
       <c r="J12">
-        <v>242.25827790673361</v>
+        <v>235.5227514444149</v>
       </c>
       <c r="K12">
-        <v>252.04316731598311</v>
+        <v>240.8900081705009</v>
       </c>
       <c r="L12">
-        <v>264.31712783220968</v>
+        <v>251.2197359451044</v>
       </c>
       <c r="M12">
-        <v>276.36357612128938</v>
+        <v>262.2417430381545</v>
       </c>
       <c r="N12">
-        <v>284.41390848817713</v>
+        <v>274.5688859176154</v>
       </c>
       <c r="O12">
-        <v>281.82827005003242</v>
+        <v>281.1388124732169</v>
       </c>
       <c r="P12">
-        <v>278.69948047890477</v>
+        <v>278.209722578946</v>
       </c>
       <c r="Q12">
-        <v>280.85327543907698</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>275.8178177420847</v>
+      </c>
+      <c r="R12">
+        <v>277.6659962366579</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>253.33009441520011</v>
+        <v>252.852134664758</v>
       </c>
       <c r="C13">
-        <v>251.0236952765959</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D13">
-        <v>248.24179530088759</v>
+        <v>251.3840259597351</v>
       </c>
       <c r="E13">
-        <v>245.90864081013919</v>
+        <v>248.3656448519052</v>
       </c>
       <c r="F13">
-        <v>243.09431772526551</v>
+        <v>246.8258413737652</v>
       </c>
       <c r="G13">
-        <v>240.82610024420731</v>
+        <v>243.7870021155041</v>
       </c>
       <c r="H13">
-        <v>242.80628979345161</v>
+        <v>242.0572219136733</v>
       </c>
       <c r="I13">
-        <v>243.90496235150599</v>
+        <v>243.9000063285451</v>
       </c>
       <c r="J13">
-        <v>250.80692957806889</v>
+        <v>245.1066898636296</v>
       </c>
       <c r="K13">
-        <v>257.08496052072007</v>
+        <v>251.7885165830296</v>
       </c>
       <c r="L13">
-        <v>270.43343025238261</v>
+        <v>257.9181637441347</v>
       </c>
       <c r="M13">
-        <v>276.37549352961781</v>
+        <v>271.4978290459294</v>
       </c>
       <c r="N13">
-        <v>280.56452018454308</v>
+        <v>276.7622152346796</v>
       </c>
       <c r="O13">
-        <v>286.41650834869068</v>
+        <v>281.5194749246966</v>
       </c>
       <c r="P13">
-        <v>292.79004430961697</v>
+        <v>286.7344221609081</v>
       </c>
       <c r="Q13">
-        <v>304.25087088864609</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>293.568927131675</v>
+      </c>
+      <c r="R13">
+        <v>303.0477082055223</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>247.92693573354779</v>
+        <v>247.6041332280797</v>
       </c>
       <c r="C14">
-        <v>283.9133271984312</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D14">
-        <v>253.22939757322069</v>
+        <v>283.8593022454741</v>
       </c>
       <c r="E14">
-        <v>238.17543688579869</v>
+        <v>253.2400843563317</v>
       </c>
       <c r="F14">
-        <v>228.8717077530373</v>
+        <v>238.2913092192338</v>
       </c>
       <c r="G14">
-        <v>227.1478643727792</v>
+        <v>228.8093434199018</v>
       </c>
       <c r="H14">
-        <v>227.30916256187871</v>
+        <v>226.8504593475583</v>
       </c>
       <c r="I14">
-        <v>230.24226040284941</v>
+        <v>227.4228362391613</v>
       </c>
       <c r="J14">
-        <v>228.87587124734321</v>
+        <v>229.9916415228223</v>
       </c>
       <c r="K14">
-        <v>235.34788900105511</v>
+        <v>229.2444868381989</v>
       </c>
       <c r="L14">
-        <v>245.79571736898171</v>
+        <v>236.3381277663102</v>
       </c>
       <c r="M14">
-        <v>248.99386067799091</v>
+        <v>246.2194785166713</v>
       </c>
       <c r="N14">
-        <v>257.42397141128021</v>
+        <v>249.8925074423544</v>
       </c>
       <c r="O14">
-        <v>259.67827276090918</v>
+        <v>257.9796467264494</v>
       </c>
       <c r="P14">
-        <v>256.20095985524478</v>
+        <v>258.9033296625776</v>
       </c>
       <c r="Q14">
-        <v>248.93981887181269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>255.7059650461014</v>
+      </c>
+      <c r="R14">
+        <v>248.3032266313058</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>249.86446424210681</v>
+        <v>250.8816166820425</v>
       </c>
       <c r="C15">
-        <v>283.99708929828682</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D15">
-        <v>253.37649583562521</v>
+        <v>284.5262217396998</v>
       </c>
       <c r="E15">
-        <v>238.27894144238391</v>
+        <v>254.304236745049</v>
       </c>
       <c r="F15">
-        <v>229.34999005367061</v>
+        <v>239.0813874565628</v>
       </c>
       <c r="G15">
-        <v>227.47914763436449</v>
+        <v>229.4708029043738</v>
       </c>
       <c r="H15">
-        <v>228.1158155754452</v>
+        <v>227.2808176943805</v>
       </c>
       <c r="I15">
-        <v>230.05681868998309</v>
+        <v>227.7920838352977</v>
       </c>
       <c r="J15">
-        <v>229.10557830958641</v>
+        <v>229.5575729265934</v>
       </c>
       <c r="K15">
-        <v>235.29760898347749</v>
+        <v>228.8677326029906</v>
       </c>
       <c r="L15">
-        <v>245.27400417042591</v>
+        <v>234.7725584772095</v>
       </c>
       <c r="M15">
-        <v>246.68466291586981</v>
+        <v>244.3857677597339</v>
       </c>
       <c r="N15">
-        <v>255.34556875090539</v>
+        <v>247.1053973429495</v>
       </c>
       <c r="O15">
-        <v>256.41280680988888</v>
+        <v>255.9142241336252</v>
       </c>
       <c r="P15">
-        <v>253.208518201641</v>
+        <v>256.4396273538571</v>
       </c>
       <c r="Q15">
-        <v>246.6219369453832</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>253.8164335729278</v>
+      </c>
+      <c r="R15">
+        <v>247.0000039350947</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>250.5434361672846</v>
+        <v>248.8726242918322</v>
       </c>
       <c r="C16">
-        <v>283.58940070408403</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D16">
-        <v>253.06392308509101</v>
+        <v>284.3142862546286</v>
       </c>
       <c r="E16">
-        <v>237.74040333986889</v>
+        <v>253.3125204360035</v>
       </c>
       <c r="F16">
-        <v>228.2220376676633</v>
+        <v>238.0884034593454</v>
       </c>
       <c r="G16">
-        <v>226.24173030868349</v>
+        <v>228.6446462556102</v>
       </c>
       <c r="H16">
-        <v>227.5544692305991</v>
+        <v>226.7846486128498</v>
       </c>
       <c r="I16">
-        <v>229.2529998366048</v>
+        <v>228.1978438268615</v>
       </c>
       <c r="J16">
-        <v>228.62418741137759</v>
+        <v>230.4490250910719</v>
       </c>
       <c r="K16">
-        <v>234.95602891471529</v>
+        <v>228.9236169181626</v>
       </c>
       <c r="L16">
-        <v>245.00109058672601</v>
+        <v>235.9865049108053</v>
       </c>
       <c r="M16">
-        <v>246.95293578212281</v>
+        <v>245.9584115825429</v>
       </c>
       <c r="N16">
-        <v>254.08914544074261</v>
+        <v>247.8266197992535</v>
       </c>
       <c r="O16">
-        <v>256.36537428357792</v>
+        <v>254.2580491540438</v>
       </c>
       <c r="P16">
-        <v>254.5934191966698</v>
+        <v>256.7666438864093</v>
       </c>
       <c r="Q16">
-        <v>249.27020117416831</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>254.7132871493665</v>
+      </c>
+      <c r="R16">
+        <v>249.2321058401676</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>248.43388523282849</v>
+        <v>251.8485834749625</v>
       </c>
       <c r="C17">
-        <v>284.35175500786079</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D17">
-        <v>253.53096702250181</v>
+        <v>284.7492304184424</v>
       </c>
       <c r="E17">
-        <v>238.62347130098681</v>
+        <v>254.3845836065963</v>
       </c>
       <c r="F17">
-        <v>228.75346868262091</v>
+        <v>240.1764132622934</v>
       </c>
       <c r="G17">
-        <v>226.79317974818079</v>
+        <v>230.2192086762697</v>
       </c>
       <c r="H17">
-        <v>227.62526751584551</v>
+        <v>228.742799101866</v>
       </c>
       <c r="I17">
-        <v>229.9131907617022</v>
+        <v>229.1192540829252</v>
       </c>
       <c r="J17">
-        <v>228.51636524797561</v>
+        <v>231.956263941139</v>
       </c>
       <c r="K17">
-        <v>235.14751284591799</v>
+        <v>230.9569946878583</v>
       </c>
       <c r="L17">
-        <v>244.7466471863813</v>
+        <v>237.8626527991377</v>
       </c>
       <c r="M17">
-        <v>246.75269076057589</v>
+        <v>248.0175551407117</v>
       </c>
       <c r="N17">
-        <v>251.287711861964</v>
+        <v>249.8301003745878</v>
       </c>
       <c r="O17">
-        <v>252.876840869695</v>
+        <v>255.3043837879934</v>
       </c>
       <c r="P17">
-        <v>248.15202506327239</v>
+        <v>257.3360575528255</v>
       </c>
       <c r="Q17">
-        <v>244.50510836489499</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>253.3800442255099</v>
+      </c>
+      <c r="R17">
+        <v>248.8156900613704</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>252.94659522604559</v>
+        <v>254.3239297066566</v>
       </c>
       <c r="C18">
-        <v>250.5020136596651</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D18">
-        <v>248.42061297377339</v>
+        <v>250.6193627146882</v>
       </c>
       <c r="E18">
-        <v>242.3661285631965</v>
+        <v>250.2997672464722</v>
       </c>
       <c r="F18">
-        <v>235.78101835779799</v>
+        <v>244.6877700188491</v>
       </c>
       <c r="G18">
-        <v>233.02227724630129</v>
+        <v>238.4102959368105</v>
       </c>
       <c r="H18">
-        <v>233.9869412425324</v>
+        <v>235.7831914072194</v>
       </c>
       <c r="I18">
-        <v>234.90567758062079</v>
+        <v>236.8201857117634</v>
       </c>
       <c r="J18">
-        <v>245.72374896318959</v>
+        <v>237.6898440590965</v>
       </c>
       <c r="K18">
-        <v>248.5954969114311</v>
+        <v>248.2415548906539</v>
       </c>
       <c r="L18">
-        <v>259.8128172601912</v>
+        <v>251.1671251890548</v>
       </c>
       <c r="M18">
-        <v>266.13552775474972</v>
+        <v>263.4418126762521</v>
       </c>
       <c r="N18">
-        <v>268.43629687939472</v>
+        <v>269.6728546780288</v>
       </c>
       <c r="O18">
-        <v>263.45091492653057</v>
+        <v>272.0319973232407</v>
       </c>
       <c r="P18">
-        <v>261.03397939225829</v>
+        <v>266.2592639541554</v>
       </c>
       <c r="Q18">
-        <v>258.53555074547808</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>262.7493597457763</v>
+      </c>
+      <c r="R18">
+        <v>260.2819301773616</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>254.02883845152579</v>
+        <v>252.1630993202065</v>
       </c>
       <c r="C19">
-        <v>250.37002774756959</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D19">
-        <v>249.23694301963349</v>
+        <v>250.1627119827502</v>
       </c>
       <c r="E19">
-        <v>245.5654979922561</v>
+        <v>249.6345238078151</v>
       </c>
       <c r="F19">
-        <v>240.89353976766151</v>
+        <v>247.0033062541902</v>
       </c>
       <c r="G19">
-        <v>233.79559792559851</v>
+        <v>242.1647713148371</v>
       </c>
       <c r="H19">
-        <v>236.49141774637479</v>
+        <v>233.9426980283041</v>
       </c>
       <c r="I19">
-        <v>239.6983515681633</v>
+        <v>236.526936376172</v>
       </c>
       <c r="J19">
-        <v>247.71041550974439</v>
+        <v>239.0138436085787</v>
       </c>
       <c r="K19">
-        <v>260.29560916798442</v>
+        <v>247.3110756992139</v>
       </c>
       <c r="L19">
-        <v>265.97701907367377</v>
+        <v>259.4471266616227</v>
       </c>
       <c r="M19">
-        <v>270.71544657633302</v>
+        <v>265.8751554723123</v>
       </c>
       <c r="N19">
-        <v>268.15815485230638</v>
+        <v>270.7701194494492</v>
       </c>
       <c r="O19">
-        <v>266.40142851715342</v>
+        <v>268.6799186056314</v>
       </c>
       <c r="P19">
-        <v>263.29306620787162</v>
+        <v>266.5677642535711</v>
       </c>
       <c r="Q19">
-        <v>267.07039840790122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>263.743134532016</v>
+      </c>
+      <c r="R19">
+        <v>267.5517815467601</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>254.37271183446401</v>
+        <v>251.6080397254015</v>
       </c>
       <c r="C20">
-        <v>249.84084111839039</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D20">
-        <v>248.90901824302961</v>
+        <v>249.7948387526689</v>
       </c>
       <c r="E20">
-        <v>243.42679499881439</v>
+        <v>247.6650231102478</v>
       </c>
       <c r="F20">
-        <v>239.38655610452861</v>
+        <v>242.4072149543566</v>
       </c>
       <c r="G20">
-        <v>235.72670714443939</v>
+        <v>237.6537171600732</v>
       </c>
       <c r="H20">
-        <v>234.70691078302221</v>
+        <v>234.6154483594313</v>
       </c>
       <c r="I20">
-        <v>240.67834815710319</v>
+        <v>234.4973299894426</v>
       </c>
       <c r="J20">
-        <v>246.37271757337331</v>
+        <v>239.7633671722259</v>
       </c>
       <c r="K20">
-        <v>259.21089190717441</v>
+        <v>244.5003496665829</v>
       </c>
       <c r="L20">
-        <v>266.74957014286582</v>
+        <v>257.4754046295748</v>
       </c>
       <c r="M20">
-        <v>263.67565509767741</v>
+        <v>265.4220103734843</v>
       </c>
       <c r="N20">
-        <v>257.11973548387152</v>
+        <v>264.0997052137378</v>
       </c>
       <c r="O20">
-        <v>257.14002387411648</v>
+        <v>257.5817167166089</v>
       </c>
       <c r="P20">
-        <v>249.10079192238379</v>
+        <v>257.0013190043721</v>
       </c>
       <c r="Q20">
-        <v>254.55856596154931</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>250.6784047158064</v>
+      </c>
+      <c r="R20">
+        <v>255.8537497761654</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>260.78041071919711</v>
+        <v>259.6655460419332</v>
       </c>
       <c r="C21">
-        <v>265.58449338177991</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D21">
-        <v>251.2811328622997</v>
+        <v>264.9626079615777</v>
       </c>
       <c r="E21">
-        <v>250.70020794551101</v>
+        <v>250.9109816711189</v>
       </c>
       <c r="F21">
-        <v>245.63149188662851</v>
+        <v>251.1003652476287</v>
       </c>
       <c r="G21">
-        <v>241.81105310764281</v>
+        <v>245.425686734154</v>
       </c>
       <c r="H21">
-        <v>241.99985870426619</v>
+        <v>243.4433543898234</v>
       </c>
       <c r="I21">
-        <v>258.09182781236899</v>
+        <v>241.5215764482434</v>
       </c>
       <c r="J21">
-        <v>266.06222382033133</v>
+        <v>259.0174488522426</v>
       </c>
       <c r="K21">
-        <v>270.0232479645021</v>
+        <v>266.4385144914368</v>
       </c>
       <c r="L21">
-        <v>278.06269541429202</v>
+        <v>268.9749282937395</v>
       </c>
       <c r="M21">
-        <v>284.65254424935029</v>
+        <v>276.2675598553712</v>
       </c>
       <c r="N21">
-        <v>297.20721887881808</v>
+        <v>283.420447705595</v>
       </c>
       <c r="O21">
-        <v>308.23279815023261</v>
+        <v>295.8090147639463</v>
       </c>
       <c r="P21">
-        <v>321.41820783268611</v>
+        <v>306.2566246448129</v>
       </c>
       <c r="Q21">
-        <v>341.76351328991421</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>317.7638640035702</v>
+      </c>
+      <c r="R21">
+        <v>337.0198530202385</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>259.11157354145018</v>
+        <v>260.2240884521334</v>
       </c>
       <c r="C22">
-        <v>265.09584404158011</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D22">
-        <v>251.2281184816911</v>
+        <v>265.3753159314517</v>
       </c>
       <c r="E22">
-        <v>251.46499525975</v>
+        <v>251.2712323950629</v>
       </c>
       <c r="F22">
-        <v>246.9758632866893</v>
+        <v>251.2465965855447</v>
       </c>
       <c r="G22">
-        <v>243.28712248137231</v>
+        <v>246.3190150219176</v>
       </c>
       <c r="H22">
-        <v>239.41810599573151</v>
+        <v>242.2335431413574</v>
       </c>
       <c r="I22">
-        <v>258.00133014748599</v>
+        <v>238.2777287342057</v>
       </c>
       <c r="J22">
-        <v>264.54769262954773</v>
+        <v>255.5640549544126</v>
       </c>
       <c r="K22">
-        <v>266.93568859557621</v>
+        <v>262.3594204872632</v>
       </c>
       <c r="L22">
-        <v>271.85200043165253</v>
+        <v>264.5685235661189</v>
       </c>
       <c r="M22">
-        <v>281.94970856487981</v>
+        <v>270.7378554358958</v>
       </c>
       <c r="N22">
-        <v>294.5253640628469</v>
+        <v>280.3385390203988</v>
       </c>
       <c r="O22">
-        <v>302.35354874291511</v>
+        <v>292.7889018764194</v>
       </c>
       <c r="P22">
-        <v>317.61288193587188</v>
+        <v>300.4081266412617</v>
       </c>
       <c r="Q22">
-        <v>337.11919253940209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>315.6625885505335</v>
+      </c>
+      <c r="R22">
+        <v>335.3332814334004</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>252.5721922732115</v>
+        <v>252.2157896327397</v>
       </c>
       <c r="C23">
-        <v>251.7475476438116</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D23">
-        <v>251.65564133921319</v>
+        <v>251.6159404209498</v>
       </c>
       <c r="E23">
-        <v>242.83215340036551</v>
+        <v>251.0376204739522</v>
       </c>
       <c r="F23">
-        <v>239.6597229607577</v>
+        <v>243.4306342433105</v>
       </c>
       <c r="G23">
-        <v>248.9155958579143</v>
+        <v>238.7255034589381</v>
       </c>
       <c r="H23">
-        <v>274.21368937143438</v>
+        <v>247.9683557565313</v>
       </c>
       <c r="I23">
-        <v>285.69788782185202</v>
+        <v>274.089319959772</v>
       </c>
       <c r="J23">
-        <v>288.5945521770073</v>
+        <v>286.8297837745945</v>
       </c>
       <c r="K23">
-        <v>297.98306640674832</v>
+        <v>289.8751730350493</v>
       </c>
       <c r="L23">
-        <v>307.86622566805318</v>
+        <v>299.4695028777441</v>
       </c>
       <c r="M23">
-        <v>321.11591992971597</v>
+        <v>309.7665021918605</v>
       </c>
       <c r="N23">
-        <v>338.88795604641098</v>
+        <v>321.734275659907</v>
       </c>
       <c r="O23">
-        <v>353.23115392892947</v>
+        <v>337.7840707367427</v>
       </c>
       <c r="P23">
-        <v>364.93578123638531</v>
+        <v>352.9262018079722</v>
       </c>
       <c r="Q23">
-        <v>385.96531326057112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>363.8187053786647</v>
+      </c>
+      <c r="R23">
+        <v>385.644309467187</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>328.08135792217962</v>
+        <v>221.389859955332</v>
       </c>
       <c r="C24">
-        <v>328.08135792217962</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D24">
-        <v>332.42151527907902</v>
+        <v>237.4788860904241</v>
       </c>
       <c r="E24">
-        <v>325.21054902321077</v>
+        <v>221.0612044446953</v>
       </c>
       <c r="F24">
-        <v>340.76933072668089</v>
+        <v>212.6825963110154</v>
       </c>
       <c r="G24">
-        <v>364.42499706968027</v>
+        <v>206.1366131232466</v>
       </c>
       <c r="H24">
-        <v>365.95755822316488</v>
+        <v>206.1087096425696</v>
       </c>
       <c r="I24">
-        <v>372.66745629723852</v>
+        <v>203.7548387995435</v>
       </c>
       <c r="J24">
-        <v>386.652905068726</v>
+        <v>205.0015594027051</v>
       </c>
       <c r="K24">
-        <v>397.32526553667611</v>
+        <v>206.974259624141</v>
       </c>
       <c r="L24">
-        <v>400.05712905005521</v>
+        <v>214.2900440120042</v>
       </c>
       <c r="M24">
-        <v>407.6576753608291</v>
+        <v>224.7409098037798</v>
       </c>
       <c r="N24">
-        <v>411.48840657311843</v>
+        <v>232.950923129941</v>
       </c>
       <c r="O24">
-        <v>430.16359459915719</v>
+        <v>248.2184826070609</v>
       </c>
       <c r="P24">
-        <v>436.91163444154222</v>
+        <v>263.1948072872566</v>
       </c>
       <c r="Q24">
-        <v>443.77129563084827</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>280.9557833434351</v>
+      </c>
+      <c r="R24">
+        <v>299.3364665037798</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>335.19200334199678</v>
+        <v>208.4961975212788</v>
       </c>
       <c r="C25">
-        <v>335.19200334199678</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D25">
-        <v>337.91305738080882</v>
+        <v>238.7351469571104</v>
       </c>
       <c r="E25">
-        <v>341.42748139699438</v>
+        <v>220.4927078201654</v>
       </c>
       <c r="F25">
-        <v>344.67615166311077</v>
+        <v>207.7127073298499</v>
       </c>
       <c r="G25">
-        <v>353.52517375400521</v>
+        <v>196.5487236418141</v>
       </c>
       <c r="H25">
-        <v>376.16364555119702</v>
+        <v>191.6834832131742</v>
       </c>
       <c r="I25">
-        <v>384.51244603570132</v>
+        <v>189.0403875019672</v>
       </c>
       <c r="J25">
-        <v>395.74655488612052</v>
+        <v>190.683757935949</v>
       </c>
       <c r="K25">
-        <v>402.7142019350124</v>
+        <v>200.1557476199346</v>
       </c>
       <c r="L25">
-        <v>412.96805167960912</v>
+        <v>201.4158102300097</v>
       </c>
       <c r="M25">
-        <v>425.23232548513192</v>
+        <v>200.9922367959278</v>
       </c>
       <c r="N25">
-        <v>436.62878458186168</v>
+        <v>214.9608692446886</v>
       </c>
       <c r="O25">
-        <v>447.32060402959331</v>
+        <v>222.5156720614389</v>
       </c>
       <c r="P25">
-        <v>455.47607461934649</v>
+        <v>238.496864475343</v>
       </c>
       <c r="Q25">
-        <v>460.07380286608122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>249.4185638175572</v>
+      </c>
+      <c r="R25">
+        <v>272.7581402412521</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>335.75273989498248</v>
+        <v>216.910658415978</v>
       </c>
       <c r="C26">
-        <v>335.10640431527702</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D26">
-        <v>336.91859989559208</v>
+        <v>234.5690859225789</v>
       </c>
       <c r="E26">
-        <v>334.25925671375239</v>
+        <v>225.7364644693172</v>
       </c>
       <c r="F26">
-        <v>334.34110060246343</v>
+        <v>211.8029556766347</v>
       </c>
       <c r="G26">
-        <v>345.14956871707381</v>
+        <v>202.0524129491801</v>
       </c>
       <c r="H26">
-        <v>352.82528503397089</v>
+        <v>201.3168397605717</v>
       </c>
       <c r="I26">
-        <v>371.81695627258011</v>
+        <v>198.6144428422687</v>
       </c>
       <c r="J26">
-        <v>377.47641943155759</v>
+        <v>197.3528296067617</v>
       </c>
       <c r="K26">
-        <v>369.41628749196991</v>
+        <v>200.7807558854883</v>
       </c>
       <c r="L26">
-        <v>367.0843608449581</v>
+        <v>214.057311771222</v>
       </c>
       <c r="M26">
-        <v>373.92193052998869</v>
+        <v>216.7027460780584</v>
       </c>
       <c r="N26">
-        <v>406.95702476146391</v>
+        <v>231.6106567298353</v>
       </c>
       <c r="O26">
-        <v>397.91011410413307</v>
+        <v>240.7456507548962</v>
       </c>
       <c r="P26">
-        <v>396.08259006371787</v>
+        <v>254.9776825029464</v>
       </c>
       <c r="Q26">
-        <v>394.37011683177951</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>273.5589986582613</v>
+      </c>
+      <c r="R26">
+        <v>288.4180184350139</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>342.22628639930548</v>
+        <v>217.9586805217816</v>
       </c>
       <c r="C27">
-        <v>340.76378236997471</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D27">
-        <v>343.82145613748878</v>
+        <v>234.8483078080305</v>
       </c>
       <c r="E27">
-        <v>346.98761374083762</v>
+        <v>226.2106383273415</v>
       </c>
       <c r="F27">
-        <v>335.9983292593663</v>
+        <v>212.3517891709209</v>
       </c>
       <c r="G27">
-        <v>349.37054013023851</v>
+        <v>202.468628561904</v>
       </c>
       <c r="H27">
-        <v>354.32187069670522</v>
+        <v>202.4885784257011</v>
       </c>
       <c r="I27">
-        <v>344.36707193660078</v>
+        <v>199.971426264502</v>
       </c>
       <c r="J27">
-        <v>358.17040853841172</v>
+        <v>199.6217913004772</v>
       </c>
       <c r="K27">
-        <v>365.48693339310501</v>
+        <v>202.0597918211246</v>
       </c>
       <c r="L27">
-        <v>375.69438417510997</v>
+        <v>213.5755166265615</v>
       </c>
       <c r="M27">
-        <v>389.86447633201419</v>
+        <v>221.4751491107927</v>
       </c>
       <c r="N27">
-        <v>398.77302995785573</v>
+        <v>233.4917953821421</v>
       </c>
       <c r="O27">
-        <v>382.21222220462312</v>
+        <v>245.5854820662706</v>
       </c>
       <c r="P27">
-        <v>392.83127694926912</v>
+        <v>249.7047308483118</v>
       </c>
       <c r="Q27">
-        <v>397.52990845769261</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>248.9014078354863</v>
+      </c>
+      <c r="R27">
+        <v>261.7155729772571</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>221.19622020976541</v>
+        <v>210.1670135307419</v>
       </c>
       <c r="C28">
-        <v>237.4354597557917</v>
-      </c>
-      <c r="D28" s="2">
-        <v>220.69295300211891</v>
+        <v>356.7702409169142</v>
+      </c>
+      <c r="D28">
+        <v>239.0670786424076</v>
       </c>
       <c r="E28">
-        <v>211.73139939565931</v>
+        <v>221.1469020291933</v>
       </c>
       <c r="F28">
-        <v>204.8102406406733</v>
+        <v>208.6396441369945</v>
       </c>
       <c r="G28">
-        <v>204.53590407411789</v>
+        <v>197.2630837018934</v>
       </c>
       <c r="H28">
-        <v>203.06917872192969</v>
+        <v>192.1034003923099</v>
       </c>
       <c r="I28">
-        <v>204.4940908785037</v>
+        <v>189.262020601214</v>
       </c>
       <c r="J28">
-        <v>206.93294170606191</v>
+        <v>190.765459111618</v>
       </c>
       <c r="K28">
-        <v>214.3400666993403</v>
+        <v>200.6894074451121</v>
       </c>
       <c r="L28">
-        <v>224.3226039017305</v>
+        <v>199.3618984541855</v>
       </c>
       <c r="M28">
-        <v>232.19093487584399</v>
+        <v>199.810275787729</v>
       </c>
       <c r="N28">
-        <v>246.96473457502699</v>
+        <v>208.8516346154971</v>
       </c>
       <c r="O28">
-        <v>262.35855626574471</v>
+        <v>223.2664730268737</v>
       </c>
       <c r="P28">
-        <v>279.50120626735122</v>
+        <v>229.240839913488</v>
       </c>
       <c r="Q28">
-        <v>298.32149046836912</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>232.5784848763883</v>
+      </c>
+      <c r="R28">
+        <v>242.4667915111962</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>208.13557063434311</v>
+        <v>208.6998628428021</v>
       </c>
       <c r="C29">
-        <v>239.02746695571051</v>
-      </c>
-      <c r="D29" s="3">
-        <v>220.92512435203011</v>
-      </c>
-      <c r="E29" s="2">
-        <v>207.96859624040499</v>
-      </c>
-      <c r="F29" s="2">
-        <v>197.56919155900081</v>
+        <v>356.7702409169142</v>
+      </c>
+      <c r="D29">
+        <v>238.7163596808113</v>
+      </c>
+      <c r="E29">
+        <v>220.8367532132126</v>
+      </c>
+      <c r="F29">
+        <v>207.7434540338747</v>
       </c>
       <c r="G29">
-        <v>192.43921578667451</v>
+        <v>196.56262885332</v>
       </c>
       <c r="H29">
-        <v>189.53204918765721</v>
+        <v>191.5761009551124</v>
       </c>
       <c r="I29">
-        <v>190.978374869795</v>
+        <v>188.7027754376358</v>
       </c>
       <c r="J29">
-        <v>201.76728862150429</v>
+        <v>190.2677645962477</v>
       </c>
       <c r="K29">
-        <v>201.9278086620287</v>
+        <v>198.4138103746403</v>
       </c>
       <c r="L29">
-        <v>201.96447872283781</v>
+        <v>198.0941831622651</v>
       </c>
       <c r="M29">
-        <v>214.24357113284671</v>
+        <v>197.9870840501503</v>
       </c>
       <c r="N29">
-        <v>222.31166065474719</v>
+        <v>205.3408166448021</v>
       </c>
       <c r="O29">
-        <v>238.34670065422199</v>
+        <v>219.5071455547908</v>
       </c>
       <c r="P29">
-        <v>248.8659517128489</v>
+        <v>227.0479474078427</v>
       </c>
       <c r="Q29">
-        <v>273.57848250407199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>231.2726296802697</v>
+      </c>
+      <c r="R29">
+        <v>238.6320217142157</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>217.952361907511</v>
+        <v>209.1026284625923</v>
       </c>
       <c r="C30">
-        <v>234.75060391527131</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D30">
-        <v>225.97601482979661</v>
-      </c>
-      <c r="E30" s="2">
-        <v>212.24846694227</v>
+        <v>238.7368219176735</v>
+      </c>
+      <c r="E30">
+        <v>220.8928425046412</v>
       </c>
       <c r="F30">
-        <v>202.64352834334201</v>
+        <v>208.4132710182272</v>
       </c>
       <c r="G30">
-        <v>201.4601015957299</v>
+        <v>196.5770540534009</v>
       </c>
       <c r="H30">
-        <v>198.71284354233561</v>
+        <v>190.7922797782484</v>
       </c>
       <c r="I30">
-        <v>198.45583808397791</v>
+        <v>188.5975358613013</v>
       </c>
       <c r="J30">
-        <v>201.39340969870199</v>
+        <v>189.159507586374</v>
       </c>
       <c r="K30">
-        <v>214.68355235391769</v>
+        <v>198.508525894643</v>
       </c>
       <c r="L30">
-        <v>217.1158806434336</v>
+        <v>198.0127808764668</v>
       </c>
       <c r="M30">
-        <v>231.78307640948981</v>
+        <v>198.0607242521864</v>
       </c>
       <c r="N30">
-        <v>241.29293087549689</v>
+        <v>205.5972718369226</v>
       </c>
       <c r="O30">
-        <v>255.8362139382518</v>
+        <v>218.1014236929481</v>
       </c>
       <c r="P30">
-        <v>274.31752805258452</v>
+        <v>225.7562447479995</v>
       </c>
       <c r="Q30">
-        <v>289.03612590356312</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>230.3809946901876</v>
+      </c>
+      <c r="R30">
+        <v>236.3567491747831</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>218.33334417990309</v>
+        <v>209.7774772542047</v>
       </c>
       <c r="C31">
-        <v>234.59837037889099</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D31">
-        <v>225.7280097818325</v>
-      </c>
-      <c r="E31" s="2">
-        <v>212.12453277685901</v>
+        <v>238.7240012544458</v>
+      </c>
+      <c r="E31">
+        <v>220.4574108565079</v>
       </c>
       <c r="F31">
-        <v>202.74042503791031</v>
+        <v>208.0886982170463</v>
       </c>
       <c r="G31">
-        <v>202.30305868974099</v>
+        <v>196.851998151731</v>
       </c>
       <c r="H31">
-        <v>199.17483494021471</v>
+        <v>192.3004644759176</v>
       </c>
       <c r="I31">
-        <v>199.20458917847029</v>
+        <v>188.8495427043898</v>
       </c>
       <c r="J31">
-        <v>201.8428748290907</v>
+        <v>190.6840095564631</v>
       </c>
       <c r="K31">
-        <v>213.3785229291565</v>
+        <v>199.5194095243465</v>
       </c>
       <c r="L31">
-        <v>221.3037302759233</v>
+        <v>198.7080477164201</v>
       </c>
       <c r="M31">
-        <v>232.61077767691509</v>
+        <v>198.1173973603198</v>
       </c>
       <c r="N31">
-        <v>244.96275854914421</v>
+        <v>204.5722428722154</v>
       </c>
       <c r="O31">
-        <v>249.2591014823214</v>
+        <v>215.750175462357</v>
       </c>
       <c r="P31">
-        <v>248.83235794043941</v>
+        <v>223.7878710789791</v>
       </c>
       <c r="Q31">
-        <v>261.14319635534019</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>228.4347028852768</v>
+      </c>
+      <c r="R31">
+        <v>230.3412855832573</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>208.9500964836262</v>
+        <v>207.4087744979858</v>
       </c>
       <c r="C32">
-        <v>238.70743723771119</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D32">
-        <v>220.65718236860141</v>
-      </c>
-      <c r="E32" s="2">
-        <v>207.75906130923471</v>
+        <v>238.0449553953922</v>
+      </c>
+      <c r="E32">
+        <v>219.8534001428102</v>
       </c>
       <c r="F32">
-        <v>196.9858071181863</v>
+        <v>206.83875294243</v>
       </c>
       <c r="G32">
-        <v>192.65445488753679</v>
+        <v>196.3773237201551</v>
       </c>
       <c r="H32">
-        <v>189.673628982411</v>
+        <v>191.280612194568</v>
       </c>
       <c r="I32">
-        <v>191.644156655995</v>
+        <v>188.8437717737522</v>
       </c>
       <c r="J32">
-        <v>200.79860417910501</v>
+        <v>189.9900891830907</v>
       </c>
       <c r="K32">
-        <v>199.85779540307979</v>
+        <v>199.1878611294198</v>
       </c>
       <c r="L32">
-        <v>199.94819218966381</v>
+        <v>198.9357862382583</v>
       </c>
       <c r="M32">
-        <v>208.0799854289406</v>
+        <v>199.4977998298358</v>
       </c>
       <c r="N32">
-        <v>222.6157502553088</v>
+        <v>210.7129621543014</v>
       </c>
       <c r="O32">
-        <v>229.02808463452459</v>
+        <v>224.012654841849</v>
       </c>
       <c r="P32">
-        <v>233.2983943537283</v>
+        <v>228.3902171952257</v>
       </c>
       <c r="Q32">
-        <v>243.41095206154449</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>232.6643703269935</v>
+      </c>
+      <c r="R32">
+        <v>247.5133412632262</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>208.38344098484029</v>
+        <v>209.7030951666601</v>
       </c>
       <c r="C33">
-        <v>238.41241580257829</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D33">
-        <v>220.56629909454389</v>
-      </c>
-      <c r="E33" s="2">
-        <v>207.45988234665421</v>
+        <v>238.8884357659643</v>
+      </c>
+      <c r="E33">
+        <v>221.1305812041196</v>
       </c>
       <c r="F33">
-        <v>196.2758587335363</v>
+        <v>208.6421270814186</v>
       </c>
       <c r="G33">
-        <v>192.09451515485631</v>
+        <v>197.3183340713852</v>
       </c>
       <c r="H33">
-        <v>189.4925604219714</v>
+        <v>192.6849010393613</v>
       </c>
       <c r="I33">
-        <v>190.70012721709679</v>
+        <v>189.9192611681832</v>
       </c>
       <c r="J33">
-        <v>199.1693287341343</v>
+        <v>191.398863801144</v>
       </c>
       <c r="K33">
-        <v>198.37662954378629</v>
+        <v>201.4145846378221</v>
       </c>
       <c r="L33">
-        <v>198.04198335401821</v>
+        <v>201.4648823728309</v>
       </c>
       <c r="M33">
-        <v>205.81237323764671</v>
+        <v>202.075903828919</v>
       </c>
       <c r="N33">
-        <v>219.32028522079921</v>
+        <v>212.0838484910072</v>
       </c>
       <c r="O33">
-        <v>226.04924870901951</v>
+        <v>226.3960160559547</v>
       </c>
       <c r="P33">
-        <v>230.4636160289653</v>
+        <v>231.5515837317981</v>
       </c>
       <c r="Q33">
-        <v>238.0711585374589</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>234.6995250082729</v>
+      </c>
+      <c r="R33">
+        <v>249.5356329694545</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>207.82199943972921</v>
+        <v>209.3748826891357</v>
       </c>
       <c r="C34">
-        <v>238.09703936270279</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D34">
-        <v>220.27130277291661</v>
-      </c>
-      <c r="E34" s="2">
-        <v>207.74368575958511</v>
+        <v>238.6959751529052</v>
+      </c>
+      <c r="E34">
+        <v>220.8310377627542</v>
       </c>
       <c r="F34">
-        <v>196.2549158982211</v>
+        <v>208.2305767108289</v>
       </c>
       <c r="G34">
-        <v>191.50033690905019</v>
+        <v>196.9029129978408</v>
       </c>
       <c r="H34">
-        <v>188.82230047608579</v>
+        <v>191.8238619811949</v>
       </c>
       <c r="I34">
-        <v>190.40560130023121</v>
+        <v>188.955717518266</v>
       </c>
       <c r="J34">
-        <v>198.82041653583889</v>
+        <v>190.1228005767196</v>
       </c>
       <c r="K34">
-        <v>198.04346390251419</v>
+        <v>199.0841088983779</v>
       </c>
       <c r="L34">
-        <v>197.96111145523091</v>
+        <v>199.379337057478</v>
       </c>
       <c r="M34">
-        <v>205.34907223220989</v>
+        <v>199.5027265974685</v>
       </c>
       <c r="N34">
-        <v>217.72428622952211</v>
+        <v>209.6726517150918</v>
       </c>
       <c r="O34">
-        <v>225.36392530081429</v>
+        <v>225.0428779093917</v>
       </c>
       <c r="P34">
-        <v>229.66682702016351</v>
+        <v>230.1064861722507</v>
       </c>
       <c r="Q34">
-        <v>236.87098588893011</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>233.5746824447046</v>
+      </c>
+      <c r="R34">
+        <v>245.4654052302776</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>208.50239203854471</v>
+        <v>208.4981144010679</v>
       </c>
       <c r="C35">
-        <v>239.09592454901289</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D35">
-        <v>221.05254361355219</v>
-      </c>
-      <c r="E35" s="2">
-        <v>208.04939712730939</v>
-      </c>
-      <c r="F35" s="2">
-        <v>196.85153029572521</v>
+        <v>238.4149809834522</v>
+      </c>
+      <c r="E35">
+        <v>220.6676541702196</v>
+      </c>
+      <c r="F35">
+        <v>207.9354839615522</v>
       </c>
       <c r="G35">
-        <v>191.98365790995959</v>
+        <v>196.8106283392877</v>
       </c>
       <c r="H35">
-        <v>188.6104477807809</v>
+        <v>191.8668761019579</v>
       </c>
       <c r="I35">
-        <v>190.05177535282161</v>
+        <v>189.5117123218726</v>
       </c>
       <c r="J35">
-        <v>198.90395409549879</v>
+        <v>190.4021626043445</v>
       </c>
       <c r="K35">
-        <v>198.0329721726664</v>
+        <v>199.647629297378</v>
       </c>
       <c r="L35">
-        <v>197.5352970992563</v>
+        <v>198.7700874720713</v>
       </c>
       <c r="M35">
-        <v>204.45749407759169</v>
+        <v>199.5045758404991</v>
       </c>
       <c r="N35">
-        <v>216.45847987944151</v>
+        <v>208.704602911473</v>
       </c>
       <c r="O35">
-        <v>224.3091461518375</v>
+        <v>222.8135157431717</v>
       </c>
       <c r="P35">
-        <v>229.5974824918878</v>
+        <v>229.300380924205</v>
       </c>
       <c r="Q35">
-        <v>231.35484057821569</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>231.522440391477</v>
+      </c>
+      <c r="R35">
+        <v>242.9815080306349</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>207.78257078376649</v>
+        <v>209.1356017430534</v>
       </c>
       <c r="C36">
-        <v>238.28938170528971</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D36">
-        <v>219.99822545582231</v>
-      </c>
-      <c r="E36" s="2">
-        <v>207.19020846397351</v>
-      </c>
-      <c r="F36" s="2">
-        <v>195.87791857611799</v>
+        <v>238.9724705636008</v>
+      </c>
+      <c r="E36">
+        <v>221.001951857777</v>
+      </c>
+      <c r="F36">
+        <v>208.3174862865495</v>
       </c>
       <c r="G36">
-        <v>191.09528486150879</v>
+        <v>197.5646423317258</v>
       </c>
       <c r="H36">
-        <v>188.4571822458341</v>
+        <v>192.1373234517018</v>
       </c>
       <c r="I36">
-        <v>189.3859903458353</v>
+        <v>189.487164797456</v>
       </c>
       <c r="J36">
-        <v>197.8236130009478</v>
+        <v>191.2612540916876</v>
       </c>
       <c r="K36">
-        <v>198.15555283390469</v>
+        <v>200.470177129189</v>
       </c>
       <c r="L36">
-        <v>198.28393167158541</v>
+        <v>200.0846382193177</v>
       </c>
       <c r="M36">
-        <v>209.4006298483736</v>
+        <v>199.608252546424</v>
       </c>
       <c r="N36">
-        <v>222.07830871847699</v>
+        <v>206.6172002695641</v>
       </c>
       <c r="O36">
-        <v>226.01989977027091</v>
+        <v>217.2204090119558</v>
       </c>
       <c r="P36">
-        <v>229.7761267546301</v>
+        <v>224.7873307358273</v>
       </c>
       <c r="Q36">
-        <v>246.48229906716611</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>228.9838548902218</v>
+      </c>
+      <c r="R36">
+        <v>232.9656132976565</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>208.39987203462391</v>
+        <v>221.0758414052381</v>
       </c>
       <c r="C37">
-        <v>239.01094773273559</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D37">
-        <v>221.17038613090489</v>
-      </c>
-      <c r="E37" s="2">
-        <v>208.10859494094501</v>
-      </c>
-      <c r="F37" s="2">
-        <v>196.72109919521219</v>
+        <v>236.0946784626112</v>
+      </c>
+      <c r="E37">
+        <v>226.1560941861166</v>
+      </c>
+      <c r="F37">
+        <v>205.1596521033209</v>
       </c>
       <c r="G37">
-        <v>192.09399563536019</v>
+        <v>201.9263031015082</v>
       </c>
       <c r="H37">
-        <v>189.16162721124689</v>
+        <v>213.9181310105295</v>
       </c>
       <c r="I37">
-        <v>190.43895687695741</v>
+        <v>218.120902807257</v>
       </c>
       <c r="J37">
-        <v>199.35399578428559</v>
+        <v>213.6998775768831</v>
       </c>
       <c r="K37">
-        <v>199.2527993036114</v>
+        <v>220.1571242776068</v>
       </c>
       <c r="L37">
-        <v>199.32198619136619</v>
+        <v>235.5522496744534</v>
       </c>
       <c r="M37">
-        <v>209.90740437367859</v>
+        <v>247.9288928711269</v>
       </c>
       <c r="N37">
-        <v>224.1550193649997</v>
+        <v>257.6030777681942</v>
       </c>
       <c r="O37">
-        <v>229.16815778474111</v>
+        <v>266.0273357422616</v>
       </c>
       <c r="P37">
-        <v>232.65121804295609</v>
+        <v>272.0332418934255</v>
       </c>
       <c r="Q37">
-        <v>247.46247540732381</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>279.4247385460965</v>
+      </c>
+      <c r="R37">
+        <v>284.08529188839</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>210.21209331449251</v>
+        <v>218.4469748548046</v>
       </c>
       <c r="C38">
-        <v>238.65009250512011</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D38">
-        <v>220.82973807576309</v>
-      </c>
-      <c r="E38" s="2">
-        <v>208.6889274135427</v>
-      </c>
-      <c r="F38" s="2">
-        <v>197.21744457026489</v>
+        <v>235.3583851515129</v>
+      </c>
+      <c r="E38">
+        <v>221.6670644219221</v>
+      </c>
+      <c r="F38">
+        <v>203.4745697833062</v>
       </c>
       <c r="G38">
-        <v>192.21568902728211</v>
+        <v>202.5917357389333</v>
       </c>
       <c r="H38">
-        <v>189.84637529796009</v>
+        <v>210.4509399478964</v>
       </c>
       <c r="I38">
-        <v>192.02753237885011</v>
+        <v>218.721572258918</v>
       </c>
       <c r="J38">
-        <v>200.84946511927231</v>
+        <v>207.2472024308888</v>
       </c>
       <c r="K38">
-        <v>199.82453695619711</v>
+        <v>214.956342659714</v>
       </c>
       <c r="L38">
-        <v>200.1587054385042</v>
+        <v>225.7152606535869</v>
       </c>
       <c r="M38">
-        <v>209.42153758112451</v>
+        <v>233.0813308895158</v>
       </c>
       <c r="N38">
-        <v>224.36420772499969</v>
+        <v>237.6095248684576</v>
       </c>
       <c r="O38">
-        <v>230.137201849674</v>
+        <v>248.4471607558166</v>
       </c>
       <c r="P38">
-        <v>233.80328140956121</v>
+        <v>260.0315874480351</v>
       </c>
       <c r="Q38">
-        <v>245.8846086977737</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>271.8179898253784</v>
+      </c>
+      <c r="R38">
+        <v>284.3237473188229</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>208.65789842323699</v>
+        <v>218.8641553946151</v>
       </c>
       <c r="C39">
-        <v>239.07172552441409</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D39">
-        <v>221.09677666905549</v>
-      </c>
-      <c r="E39" s="2">
-        <v>208.50316613663489</v>
-      </c>
-      <c r="F39" s="2">
-        <v>197.13513274788039</v>
+        <v>234.5681439371987</v>
+      </c>
+      <c r="E39">
+        <v>220.1006047250343</v>
+      </c>
+      <c r="F39">
+        <v>202.2379552585147</v>
       </c>
       <c r="G39">
-        <v>192.18941537181209</v>
+        <v>201.4199046041671</v>
       </c>
       <c r="H39">
-        <v>189.54911455927811</v>
+        <v>206.82589426204</v>
       </c>
       <c r="I39">
-        <v>190.88163672876581</v>
+        <v>212.0765406164688</v>
       </c>
       <c r="J39">
-        <v>199.22911138680749</v>
+        <v>205.5689468550628</v>
       </c>
       <c r="K39">
-        <v>198.70444212652799</v>
+        <v>213.1526505871172</v>
       </c>
       <c r="L39">
-        <v>198.57892306474599</v>
+        <v>223.8195405238054</v>
       </c>
       <c r="M39">
-        <v>208.91863875882581</v>
+        <v>235.1520438755131</v>
       </c>
       <c r="N39">
-        <v>223.68895077475599</v>
+        <v>243.2769818142873</v>
       </c>
       <c r="O39">
-        <v>230.49314627203469</v>
+        <v>255.0601158398006</v>
       </c>
       <c r="P39">
-        <v>234.00636917758379</v>
+        <v>261.2120006087501</v>
       </c>
       <c r="Q39">
-        <v>246.26050754648139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>263.9699576277603</v>
+      </c>
+      <c r="R39">
+        <v>272.052820505973</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>208.37160112380741</v>
+        <v>245.4097012009393</v>
       </c>
       <c r="C40">
-        <v>238.5878685314411</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D40">
-        <v>220.32058030526949</v>
-      </c>
-      <c r="E40" s="2">
-        <v>207.5794692712407</v>
-      </c>
-      <c r="F40" s="2">
-        <v>196.50965853504539</v>
+        <v>246.2802634886876</v>
+      </c>
+      <c r="E40">
+        <v>244.0010998483044</v>
+      </c>
+      <c r="F40">
+        <v>236.7527951679689</v>
       </c>
       <c r="G40">
-        <v>192.27492623889981</v>
+        <v>227.7966979524384</v>
       </c>
       <c r="H40">
-        <v>188.59269790171749</v>
+        <v>215.5899849929741</v>
       </c>
       <c r="I40">
-        <v>190.2636633219891</v>
+        <v>215.9676253987411</v>
       </c>
       <c r="J40">
-        <v>199.06255037998241</v>
+        <v>225.9576329428311</v>
       </c>
       <c r="K40">
-        <v>198.8472745027201</v>
+        <v>230.8769441508066</v>
       </c>
       <c r="L40">
-        <v>197.9369547198051</v>
+        <v>238.6168782635349</v>
       </c>
       <c r="M40">
-        <v>204.63424532911671</v>
+        <v>250.682507893398</v>
       </c>
       <c r="N40">
-        <v>216.45760596915849</v>
+        <v>267.7224501203331</v>
       </c>
       <c r="O40">
-        <v>224.45272026043639</v>
+        <v>285.7486880586659</v>
       </c>
       <c r="P40">
-        <v>228.84350155986431</v>
+        <v>297.8079442739354</v>
       </c>
       <c r="Q40">
-        <v>232.67154850555829</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>311.8776545972264</v>
+      </c>
+      <c r="R40">
+        <v>325.5293394172375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>219.9895214989441</v>
+        <v>252.2694501139243</v>
       </c>
       <c r="C41">
-        <v>235.6357007508455</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D41">
-        <v>224.82694698660691</v>
-      </c>
-      <c r="E41" s="2">
-        <v>205.17205877141851</v>
-      </c>
-      <c r="F41" s="2">
-        <v>201.64924137293141</v>
+        <v>252.2571609761901</v>
+      </c>
+      <c r="E41">
+        <v>245.1271314464287</v>
+      </c>
+      <c r="F41">
+        <v>256.9349335590905</v>
       </c>
       <c r="G41">
-        <v>214.29681833144531</v>
+        <v>271.4076572840264</v>
       </c>
       <c r="H41">
-        <v>217.41211481651359</v>
+        <v>285.6200376493042</v>
       </c>
       <c r="I41">
-        <v>212.7101162499329</v>
+        <v>283.6437248146351</v>
       </c>
       <c r="J41">
-        <v>218.5486769379562</v>
+        <v>275.9988368902451</v>
       </c>
       <c r="K41">
-        <v>233.38584878670409</v>
+        <v>272.5271110061091</v>
       </c>
       <c r="L41">
-        <v>245.7967937155953</v>
+        <v>273.8230323851303</v>
       </c>
       <c r="M41">
-        <v>255.2944981426692</v>
+        <v>285.7491783229455</v>
       </c>
       <c r="N41">
-        <v>264.03922681012409</v>
+        <v>305.1656535985986</v>
       </c>
       <c r="O41">
-        <v>269.64322294438671</v>
+        <v>314.6585460311689</v>
       </c>
       <c r="P41">
-        <v>277.16443158788542</v>
+        <v>320.7554391452434</v>
       </c>
       <c r="Q41">
-        <v>281.78771960321632</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>329.6844265319633</v>
+      </c>
+      <c r="R41">
+        <v>330.4269015545022</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>218.55411666699371</v>
+        <v>258.7250868755594</v>
       </c>
       <c r="C42">
-        <v>235.44532479397279</v>
-      </c>
-      <c r="D42" s="2">
-        <v>221.21358584736561</v>
-      </c>
-      <c r="E42" s="2">
-        <v>202.69368669688029</v>
+        <v>356.7702409169142</v>
+      </c>
+      <c r="D42">
+        <v>262.8211254791903</v>
+      </c>
+      <c r="E42">
+        <v>246.7124467208999</v>
       </c>
       <c r="F42">
-        <v>201.4275468873679</v>
+        <v>251.8816693384026</v>
       </c>
       <c r="G42">
-        <v>210.31296520667161</v>
+        <v>250.9026619406457</v>
       </c>
       <c r="H42">
-        <v>216.65311084547409</v>
+        <v>251.8497924355294</v>
       </c>
       <c r="I42">
-        <v>205.0742950418402</v>
+        <v>248.1145882458507</v>
       </c>
       <c r="J42">
-        <v>211.81427940385521</v>
+        <v>243.1628840780439</v>
       </c>
       <c r="K42">
-        <v>222.48904610392009</v>
+        <v>255.1227077850907</v>
       </c>
       <c r="L42">
-        <v>229.47145425269619</v>
+        <v>264.9069530839046</v>
       </c>
       <c r="M42">
-        <v>234.17043223333869</v>
+        <v>278.6051588011654</v>
       </c>
       <c r="N42">
-        <v>244.8646663532171</v>
+        <v>284.1041268325259</v>
       </c>
       <c r="O42">
-        <v>256.11246591502629</v>
+        <v>285.5557969324893</v>
       </c>
       <c r="P42">
-        <v>268.49540993708843</v>
+        <v>290.2351302941129</v>
       </c>
       <c r="Q42">
-        <v>280.79130345023282</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>294.775101345138</v>
+      </c>
+      <c r="R42">
+        <v>301.2809670611122</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>218.00568111810881</v>
+        <v>250.3298209985897</v>
       </c>
       <c r="C43">
-        <v>234.95261002273691</v>
+        <v>356.7702409169142</v>
       </c>
       <c r="D43">
-        <v>220.29419875061171</v>
-      </c>
-      <c r="E43" s="2">
-        <v>202.83972055576021</v>
-      </c>
-      <c r="F43" s="2">
-        <v>201.2623650979364</v>
+        <v>245.9291060514178</v>
+      </c>
+      <c r="E43">
+        <v>252.9874375521994</v>
+      </c>
+      <c r="F43">
+        <v>257.0712488628865</v>
       </c>
       <c r="G43">
-        <v>206.35282907963989</v>
+        <v>265.0508069401117</v>
       </c>
       <c r="H43">
-        <v>213.19073682424269</v>
+        <v>277.0819608177211</v>
       </c>
       <c r="I43">
-        <v>207.015309746127</v>
+        <v>275.4686812255698</v>
       </c>
       <c r="J43">
-        <v>214.97829251340059</v>
+        <v>253.2192927088948</v>
       </c>
       <c r="K43">
-        <v>226.21331746171461</v>
+        <v>249.0945042406584</v>
       </c>
       <c r="L43">
-        <v>237.87774856935971</v>
+        <v>256.9129065099477</v>
       </c>
       <c r="M43">
-        <v>246.06392741254231</v>
+        <v>271.5144208782743</v>
       </c>
       <c r="N43">
-        <v>260.67043242913837</v>
+        <v>276.487080691959</v>
       </c>
       <c r="O43">
-        <v>266.31384335550479</v>
+        <v>280.6440003191923</v>
       </c>
       <c r="P43">
-        <v>268.71159502660993</v>
+        <v>283.0151773694959</v>
       </c>
       <c r="Q43">
-        <v>277.37514683444653</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44">
-        <v>245.56603292326619</v>
-      </c>
-      <c r="C44">
-        <v>246.3289588357465</v>
-      </c>
-      <c r="D44">
-        <v>245.7619751654411</v>
-      </c>
-      <c r="E44">
-        <v>238.11855747084121</v>
-      </c>
-      <c r="F44">
-        <v>228.64756491601949</v>
-      </c>
-      <c r="G44">
-        <v>217.46876633668771</v>
-      </c>
-      <c r="H44">
-        <v>217.76240384978789</v>
-      </c>
-      <c r="I44">
-        <v>229.27831020948369</v>
-      </c>
-      <c r="J44">
-        <v>234.3204090132578</v>
-      </c>
-      <c r="K44">
-        <v>241.7640470789128</v>
-      </c>
-      <c r="L44">
-        <v>254.12860171565029</v>
-      </c>
-      <c r="M44">
-        <v>271.06368926847739</v>
-      </c>
-      <c r="N44">
-        <v>289.41141492945133</v>
-      </c>
-      <c r="O44">
-        <v>301.68646861789568</v>
-      </c>
-      <c r="P44">
-        <v>315.9946644536771</v>
-      </c>
-      <c r="Q44">
-        <v>329.49210165800122</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45">
-        <v>251.97452497124351</v>
-      </c>
-      <c r="C45">
-        <v>251.93764025136539</v>
-      </c>
-      <c r="D45">
-        <v>244.77463405696491</v>
-      </c>
-      <c r="E45">
-        <v>256.26073073453807</v>
-      </c>
-      <c r="F45">
-        <v>269.75932563721022</v>
-      </c>
-      <c r="G45">
-        <v>282.74181947192568</v>
-      </c>
-      <c r="H45">
-        <v>281.94943188530061</v>
-      </c>
-      <c r="I45">
-        <v>274.71653786101132</v>
-      </c>
-      <c r="J45">
-        <v>272.52011535218048</v>
-      </c>
-      <c r="K45">
-        <v>272.29209330157369</v>
-      </c>
-      <c r="L45">
-        <v>285.24714383414721</v>
-      </c>
-      <c r="M45">
-        <v>303.95141688360582</v>
-      </c>
-      <c r="N45">
-        <v>314.14073486838328</v>
-      </c>
-      <c r="O45">
-        <v>320.74660950861937</v>
-      </c>
-      <c r="P45">
-        <v>329.53494027191539</v>
-      </c>
-      <c r="Q45">
-        <v>330.02266530441051</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B46">
-        <v>258.20625503178331</v>
-      </c>
-      <c r="C46">
-        <v>262.28603024192103</v>
-      </c>
-      <c r="D46">
-        <v>246.03448513787899</v>
-      </c>
-      <c r="E46">
-        <v>251.7588677354172</v>
-      </c>
-      <c r="F46">
-        <v>249.8458341910958</v>
-      </c>
-      <c r="G46">
-        <v>250.36384914187289</v>
-      </c>
-      <c r="H46">
-        <v>246.38638253431139</v>
-      </c>
-      <c r="I46">
-        <v>241.35737357128411</v>
-      </c>
-      <c r="J46">
-        <v>252.44182921353749</v>
-      </c>
-      <c r="K46">
-        <v>262.24998358463853</v>
-      </c>
-      <c r="L46">
-        <v>276.45149015606762</v>
-      </c>
-      <c r="M46">
-        <v>280.97508974810933</v>
-      </c>
-      <c r="N46">
-        <v>282.67424209884268</v>
-      </c>
-      <c r="O46">
-        <v>287.29696670698519</v>
-      </c>
-      <c r="P46">
-        <v>292.73376495034557</v>
-      </c>
-      <c r="Q46">
-        <v>297.92269383290989</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47">
-        <v>247.64235309670559</v>
-      </c>
-      <c r="C47">
-        <v>245.03440038502151</v>
-      </c>
-      <c r="D47">
-        <v>251.49773845173189</v>
-      </c>
-      <c r="E47">
-        <v>255.15880463461161</v>
-      </c>
-      <c r="F47">
-        <v>263.12443789334128</v>
-      </c>
-      <c r="G47">
-        <v>275.81551800874257</v>
-      </c>
-      <c r="H47">
-        <v>273.14806534918262</v>
-      </c>
-      <c r="I47">
-        <v>252.36382881190701</v>
-      </c>
-      <c r="J47">
-        <v>247.47395174403499</v>
-      </c>
-      <c r="K47">
-        <v>254.18140180493401</v>
-      </c>
-      <c r="L47">
-        <v>269.56955782750049</v>
-      </c>
-      <c r="M47">
-        <v>274.33839755725847</v>
-      </c>
-      <c r="N47">
-        <v>278.00656984491832</v>
-      </c>
-      <c r="O47">
-        <v>279.26928837223528</v>
-      </c>
-      <c r="P47">
-        <v>278.13441129280147</v>
-      </c>
-      <c r="Q47">
-        <v>278.42171613103221</v>
+        <v>282.4231415642337</v>
+      </c>
+      <c r="R43">
+        <v>281.572692500556</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>